--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$G$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$G$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Build number</t>
+          <t>Artifact under test (standard / accelerated)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -552,7 +552,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Commit / tag</t>
+          <t>Build number</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -560,7 +560,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Commit / tag</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -568,7 +568,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Tester</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -576,7 +576,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>OS / version</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>GPU / driver</t>
+          <t>OS / version</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -592,17 +592,20 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>GPU / driver</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Display scaling (DPI)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Steps passed</t>
-        </is>
-      </c>
       <c r="B13">
         <f>COUNTIF(Run!F:F,"PASS")</f>
         <v/>
@@ -611,7 +614,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Steps failed</t>
+          <t>Steps passed</t>
         </is>
       </c>
       <c r="B14">
@@ -622,7 +625,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Steps blocked / N-A</t>
+          <t>Steps failed</t>
         </is>
       </c>
       <c r="B15">
@@ -630,59 +633,81 @@
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Release decision (SHIP / HOLD)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Steps blocked / N-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>Release decision (SHIP / HOLD)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Decision rationale</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Automated gates that must ALSO be green for this release (these are not manual steps):</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>fractadyne --selftest            -&gt; checks 139/139, goldens 17/17</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>python validation/corpus/generate_corpus.py --check  -&gt; 38/38 MATCH</t>
+          <t>fractadyne --selftest            -&gt; exit 0. At 0.2.40: 140/140 checks, 18/18 goldens.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fractadyne --livetest tours/grand-tour.toml --size 480x270  -&gt; 24/24, 0 drifted</t>
+          <t xml:space="preserve">   (The run prints its own totals. A DIFFERENT total is not automatically a failure,</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fractadyne --motiontest          -&gt; VERDICT PASS</t>
+          <t xml:space="preserve">    but it must be explained - a silently skipped check looks exactly like a pass.)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>python validation/corpus/generate_corpus.py --check  -&gt; 38/38 MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fractadyne --livetest tours/grand-tour.toml --size 480x270  -&gt; 24/24, 0 drifted</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fractadyne --motiontest          -&gt; VERDICT PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>cargo build --release            -&gt; warning-free</t>
         </is>
@@ -702,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2924,7 +2949,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location).</t>
+          <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location), including a 'Deep-zoom arithmetic' line naming the backend in use.</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr"/>
@@ -2942,12 +2967,12 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Report an issue… </t>
+          <t>Help &gt; About (the last Help section). Read the 'Deep-zoom arithmetic' line.</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
+          <t>Names the arithmetic that has actually run and what the build contains. On the standard build: astro-float. On the accelerated build: rug, with the MPFR/GMP versions. Before any deep render it may say none has run yet - that is correct, not a missing value.</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr"/>
@@ -2965,12 +2990,12 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; Check for updates.</t>
+          <t xml:space="preserve">Help &gt; Faster deep zoom… </t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
+          <t>On the STANDARD build: explains the optional accelerated download and offers two buttons. 'Download for this version' opens a URL containing THIS version's tag; 'All releases' opens the releases page. On the ACCELERATED build: says you are already running it instead, and offers no download.</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr"/>
@@ -2988,12 +3013,12 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Settings - change a setting, close and reopen the menu.</t>
+          <t xml:space="preserve">Help &gt; Report an issue… </t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Setting persists and takes effect.</t>
+          <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr"/>
@@ -3001,35 +3026,45 @@
       <c r="G104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Persistence</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="n"/>
-      <c r="C105" s="6" t="n"/>
-      <c r="D105" s="6" t="n"/>
-      <c r="E105" s="6" t="n"/>
-      <c r="F105" s="6" t="n"/>
-      <c r="G105" s="7" t="n"/>
+      <c r="A105" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Help &amp; settings</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Help &gt; Check for updates.</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr"/>
+      <c r="G105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+          <t>File &gt; Settings - change a setting, close and reopen the menu.</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
+          <t>Setting persists and takes effect.</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr"/>
@@ -3037,27 +3072,17 @@
       <c r="G106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>Persistence</t>
-        </is>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>Relaunch the app.</t>
-        </is>
-      </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr"/>
-      <c r="F107" s="8" t="inlineStr"/>
-      <c r="G107" s="9" t="inlineStr"/>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="n"/>
+      <c r="E107" s="6" t="n"/>
+      <c r="F107" s="6" t="n"/>
+      <c r="G107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
@@ -3065,17 +3090,17 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Check config\logs for crash-*.txt files created during this run.</t>
+          <t>Extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
+          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr"/>
@@ -3083,35 +3108,45 @@
       <c r="G108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
-      <c r="G109" s="7" t="n"/>
+      <c r="A109" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>Help &gt; About on that build.</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr"/>
+      <c r="G109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+          <t>Check that your existing locations, bookmarks and last session are present.</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
+          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr"/>
@@ -3120,21 +3155,21 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
+          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr"/>
@@ -3143,21 +3178,21 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>No crash and no stuck frame; the final selection is what renders.</t>
+          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr"/>
@@ -3165,62 +3200,250 @@
       <c r="G112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="8" t="n">
+        <v>99</v>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after.</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Fails to start with a missing-DLL error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr"/>
+      <c r="F113" s="8" t="inlineStr"/>
+      <c r="G113" s="9" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="F114" s="6" t="n"/>
+      <c r="G114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr"/>
+      <c r="F115" s="8" t="inlineStr"/>
+      <c r="G115" s="9" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n">
+        <v>101</v>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>Relaunch the app.</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr"/>
+      <c r="F116" s="8" t="inlineStr"/>
+      <c r="G116" s="9" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Check config\logs for crash-*.txt files created during this run.</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr"/>
+      <c r="F117" s="8" t="inlineStr"/>
+      <c r="G117" s="9" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="n"/>
+      <c r="F118" s="6" t="n"/>
+      <c r="G118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr"/>
+      <c r="F119" s="8" t="inlineStr"/>
+      <c r="G119" s="9" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr"/>
+      <c r="F120" s="8" t="inlineStr"/>
+      <c r="G120" s="9" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>No crash and no stuck frame; the final selection is what renders.</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr"/>
+      <c r="F121" s="8" t="inlineStr"/>
+      <c r="G121" s="9" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-      <c r="E113" s="6" t="n"/>
-      <c r="F113" s="6" t="n"/>
-      <c r="G113" s="7" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="6" t="n"/>
+      <c r="F122" s="6" t="n"/>
+      <c r="G122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>Sign-off</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr"/>
-      <c r="F114" s="8" t="inlineStr"/>
-      <c r="G114" s="9" t="inlineStr"/>
+      <c r="E123" s="9" t="inlineStr"/>
+      <c r="F123" s="8" t="inlineStr"/>
+      <c r="G123" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G114"/>
-  <mergeCells count="15">
+  <autoFilter ref="A1:G123"/>
+  <mergeCells count="16">
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A118:G118"/>
+    <mergeCell ref="A122:G122"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A105:G105"/>
-    <mergeCell ref="A109:G109"/>
+    <mergeCell ref="A114:G114"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A86:G86"/>
     <mergeCell ref="A92:G92"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A113:G113"/>
     <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A107:G107"/>
     <mergeCell ref="A99:G99"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="F2:F123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$G$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAD6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2DCDB"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,6 +160,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -605,12 +629,6 @@
       </c>
       <c r="B12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="B13">
-        <f>COUNTIF(Run!F:F,"PASS")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -618,7 +636,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF(Run!F:F,"FAIL")</f>
+        <f>COUNTIF(Run!G:G,"PASS")</f>
         <v/>
       </c>
     </row>
@@ -629,7 +647,7 @@
         </is>
       </c>
       <c r="B15">
-        <f>COUNTIF(Run!F:F,"BLOCKED")+COUNTIF(Run!F:F,"N-A")</f>
+        <f>COUNTIF(Run!G:G,"FAIL")</f>
         <v/>
       </c>
     </row>
@@ -639,7 +657,10 @@
           <t>Steps blocked / N-A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16">
+        <f>COUNTIF(Run!G:G,"BLOCKED")+COUNTIF(Run!G:G,"N-A")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -667,7 +688,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fractadyne --selftest            -&gt; exit 0. At 0.2.40: 140/140 checks, 18/18 goldens.</t>
+          <t>fractadyne --selftest            -&gt; exit 0. At 0.2.40: 168/168 checks, 18/18 goldens.</t>
         </is>
       </c>
     </row>
@@ -688,28 +709,112 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>python validation/corpus/generate_corpus.py --check  -&gt; 38/38 MATCH</t>
+          <t>fractadyne --uitest DIR          -&gt; 29/29 steps, no-crash-files PASS, exit 0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fractadyne --livetest tours/grand-tour.toml --size 480x270  -&gt; 24/24, 0 drifted</t>
+          <t>fractadyne --soak 300            -&gt; soak-liveness PASS (frames advance, memory holds)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fractadyne --motiontest          -&gt; VERDICT PASS</t>
+          <t>python validation/corpus/generate_corpus.py --check  -&gt; 38/38 MATCH</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>fractadyne --livetest tours/grand-tour.toml --size 480x270  -&gt; 24/24, 0 drifted</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fractadyne --motiontest          -&gt; VERDICT PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cargo test --workspace --release -&gt; all green</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>cargo build --release            -&gt; warning-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>python scripts/checklist_coverage.py -&gt; exit 0 (no row claims coverage it lacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>How much of the Run sheet is machine-checked:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>70 of 106 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Perform these as a SPOT CHECK: confirm the feature is there and looks right, and move on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>32 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3 need a person outright, and 1 is a process step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>The 'Automated by' column on each row says which, and names the check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A row still FAILS on your judgement even when it says AUTO - the machine checks that the</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   image is not blank, never that it is beautiful.</t>
         </is>
       </c>
     </row>
@@ -727,16 +832,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -762,15 +868,20 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>Automated by</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Actual result</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Pass/Fail</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -787,7 +898,8 @@
       <c r="D2" s="6" t="n"/>
       <c r="E2" s="6" t="n"/>
       <c r="F2" s="6" t="n"/>
-      <c r="G2" s="7" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
@@ -808,9 +920,15 @@
           <t>Window opens within a few seconds. No console errors. No crash dialog.</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: no-crash-files
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -831,9 +949,14 @@
           <t>Shows 'Fractadyne v&lt;version&gt; (build &lt;n&gt;)' and the version matches the release being tested.</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: title_string_matches_version</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -854,9 +977,14 @@
           <t>Dialog is readable, no clipped text, buttons work, and it closes without reappearing.</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: welcome_shows_once</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -877,9 +1005,14 @@
           <t>The full Mandelbrot set is drawn, centred, correctly proportioned, and finishes rendering (no permanent blank, black, or half-drawn frame).</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: home</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -892,7 +1025,8 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -913,9 +1047,14 @@
           <t>All five regions present. Nothing overlaps, is cut off, or spills outside the window.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: layout-regions</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -936,9 +1075,15 @@
           <t>Text is crisp and fully legible at the current DPI. Icons are not blurry, clipped or missing (no placeholder boxes).</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: every_ui_glyph_has_a_font_that_can_draw_it
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -959,9 +1104,15 @@
           <t>Consistent theme throughout. Sufficient contrast to read every label. Active/selected states are visually distinct.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: theme_contrast_meets_minimum
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -982,9 +1133,14 @@
           <t>Shows centre coordinates, cursor position, zoom, and iteration count. Values are populated, not blank or placeholder.</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="9" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: status-bar-populated</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1002,12 +1158,17 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>All sections expand and collapse. No empty sections. Controls are aligned and fully visible.</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
+          <t>All sections expand and collapse. No empty sections. Controls are aligned and fully visible. (Not automated: the harness does not drive individual CollapsingHeaders. The panel's presence and non-overlap ARE checked by uitest:layout-regions.)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1028,9 +1189,14 @@
           <t>Panel hides, the fractal area reflows to use the space, and re-enabling restores it with settings intact.</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="9" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: panel-toggle-reflows</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1043,7 +1209,8 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="7" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -1064,9 +1231,15 @@
           <t>The fractal re-renders to the new aspect ratio without stretching or distortion. The panel and status bar stay usable. No crash.</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: layout-regions
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -1087,9 +1260,15 @@
           <t>Layout still holds; no controls become unreachable; the image stays correctly proportioned.</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: layout-regions
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -1110,9 +1289,14 @@
           <t>Renders at the new size both ways. No lingering black bands or stale image.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="9" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: window-maximize-restore</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -1133,9 +1317,14 @@
           <t>App stays responsive and recovers to a correct, complete frame. No crash, no permanently blank view.</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="9" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: window-rapid-resize</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -1156,9 +1345,14 @@
           <t>UI rescales and stays legible; the image re-renders correctly.</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="9" t="inlineStr"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1171,7 +1365,8 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -1192,9 +1387,15 @@
           <t>View zooms in centred on the clicked point by the selected Factor. Motion is smooth and lands where you clicked.</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: click_zoom_applies_factor
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -1215,9 +1416,15 @@
           <t>Each factor visibly changes the zoom step. The status-bar zoom value increases accordingly.</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: click_zoom_applies_factor
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -1238,9 +1445,15 @@
           <t>Zoom in and out both work and are centred on the view.</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: toolbar_zoom_actions
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
@@ -1261,9 +1474,15 @@
           <t>The image follows the cursor 1:1 while dragging and resolves to a sharp frame when released.</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: pan_pixels_moves_exactly_one_pixel_per_pixel
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -1284,9 +1503,15 @@
           <t>Wheel zooms in/out smoothly about the cursor.</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="9" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: zoom_at_keeps_the_point_under_the_cursor_fixed
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
@@ -1307,9 +1532,14 @@
           <t>Undo steps back through the previous views; redo returns forward. Coordinates match what you visited.</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="9" t="inlineStr"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: undo_redo_round_trip</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
@@ -1330,9 +1560,14 @@
           <t>Returns to the whole set, animated, ending at the standard home view.</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="9" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: home_view_is_the_default</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
@@ -1353,9 +1588,14 @@
           <t>Instantly returns to the default view for the current fractal.</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="9" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: reset_view_is_the_default</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -1376,9 +1616,15 @@
           <t>Minimap appears, shows the current viewport indicator, and tracks your navigation.</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="9" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: minimap_drag_signs
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1391,7 +1637,8 @@
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
       <c r="F30" s="6" t="n"/>
-      <c r="G30" s="7" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -1412,9 +1659,15 @@
           <t>Detail keeps resolving. No banding artefacts, no blocky tiles left behind, no all-black frames.</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: depth-ladder-coherent
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
@@ -1435,9 +1688,14 @@
           <t>Mode changes as depth increases (direct -&gt; perturb df32 -&gt; floatexp). Each transition is seamless; the image does not flash to garbage or flat colour.</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="9" t="inlineStr"/>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: zoom-sequence across direct→df32 seam</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
@@ -1458,9 +1716,14 @@
           <t>Image still resolves to clean structure. Status bar precision and orbit length grow. No speckle field, no solid-colour frame.</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="9" t="inlineStr"/>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: depth-ladder-coherent</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -1481,9 +1744,14 @@
           <t>Still renders real structure. Deep zoom is the headline feature; a blank or noise frame here is a release blocker.</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: extreme-depth-coherent</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
@@ -1504,9 +1772,15 @@
           <t>The exterior shows smooth colour bands, NOT per-pixel salt-and-pepper speckle.</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="9" t="inlineStr"/>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: normalize-reduces-speckle
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -1527,9 +1801,15 @@
           <t>The exterior becomes visibly noisier/aliased - which confirms the setting is actually doing something. Turn it back ON.</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="9" t="inlineStr"/>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: normalize-reduces-speckle
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
@@ -1550,9 +1830,15 @@
           <t>Panning stays responsive, and the frame resolves fully afterwards rather than staying coarse.</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="9" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: pan consistency
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
@@ -1573,9 +1859,14 @@
           <t>No freeze, no crash, no device-loss dialog. The app remains responsive throughout.</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="9" t="inlineStr"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --autodive-home</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1588,7 +1879,8 @@
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="n"/>
       <c r="F39" s="6" t="n"/>
-      <c r="G39" s="7" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
@@ -1609,9 +1901,14 @@
           <t>Correct, recognisable Mandelbrot renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="9" t="inlineStr"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: home</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
@@ -1632,9 +1929,14 @@
           <t>Correct, recognisable Multibrot3 renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="9" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: multibrot3</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
@@ -1655,9 +1957,14 @@
           <t>Correct, recognisable Multibrot4 renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="9" t="inlineStr"/>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: multibrot4</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
@@ -1678,9 +1985,14 @@
           <t>Correct, recognisable Multibrot5 renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr"/>
-      <c r="G43" s="9" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: multibrot5</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
@@ -1701,9 +2013,14 @@
           <t>Correct, recognisable Tricorn renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="9" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: tricorn</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr"/>
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
@@ -1724,9 +2041,14 @@
           <t>Correct, recognisable Burning Ship renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="8" t="inlineStr"/>
-      <c r="G45" s="9" t="inlineStr"/>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: burning-ship</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
@@ -1747,9 +2069,14 @@
           <t>Correct, recognisable Celtic renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
-      <c r="G46" s="9" t="inlineStr"/>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: celtic</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
@@ -1770,9 +2097,14 @@
           <t>Correct, recognisable Buffalo renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr"/>
-      <c r="G47" s="9" t="inlineStr"/>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: buffalo</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
@@ -1793,9 +2125,14 @@
           <t>Correct, recognisable Phoenix renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="9" t="inlineStr"/>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: phoenix</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
@@ -1816,9 +2153,14 @@
           <t>Correct, recognisable Newton renders at a sensible default view. No blank frame, no error.</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="8" t="inlineStr"/>
-      <c r="G49" s="9" t="inlineStr"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: newton</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr"/>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -1839,9 +2181,14 @@
           <t>Detail resolves correctly for that formula, not just for Mandelbrot.</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="8" t="inlineStr"/>
-      <c r="G50" s="9" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: multibrot3-1e6</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
@@ -1862,9 +2209,14 @@
           <t>A Julia set renders for the current c. Image is plausible and complete.</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="8" t="inlineStr"/>
-      <c r="G51" s="9" t="inlineStr"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: julia-coherent</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
@@ -1885,9 +2237,15 @@
           <t>Window splits. Left shows the parameter set; right shows the Julia set for the cursor's c and updates as you move.</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="8" t="inlineStr"/>
-      <c r="G52" s="9" t="inlineStr"/>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: dual_view_splits_the_viewports
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr"/>
+      <c r="G52" s="8" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
@@ -1908,9 +2266,15 @@
           <t>The Julia side zooms independently and resolves correctly.</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="8" t="inlineStr"/>
-      <c r="G53" s="9" t="inlineStr"/>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: julia_viewport_zooms_independently
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
@@ -1931,9 +2295,14 @@
           <t>Returns cleanly to the single Mandelbrot view.</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr"/>
-      <c r="F54" s="8" t="inlineStr"/>
-      <c r="G54" s="9" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: leaving_dual_restores_the_single_view</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -1946,7 +2315,8 @@
       <c r="D55" s="6" t="n"/>
       <c r="E55" s="6" t="n"/>
       <c r="F55" s="6" t="n"/>
-      <c r="G55" s="7" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
@@ -1967,9 +2337,14 @@
           <t>Colouring visibly changes and produces a coherent image (no all-black, all-white, or uniform flat frame).</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="8" t="inlineStr"/>
-      <c r="G56" s="9" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: colour methods are all different</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr"/>
+      <c r="G56" s="8" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
@@ -1990,9 +2365,14 @@
           <t>Colouring visibly changes and produces a coherent image (no all-black, all-white, or uniform flat frame).</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="8" t="inlineStr"/>
-      <c r="G57" s="9" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: colour methods are all different</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr"/>
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
@@ -2013,9 +2393,14 @@
           <t>Colouring visibly changes and produces a coherent image (no all-black, all-white, or uniform flat frame).</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr"/>
-      <c r="F58" s="8" t="inlineStr"/>
-      <c r="G58" s="9" t="inlineStr"/>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: colour methods are all different</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
@@ -2036,9 +2421,14 @@
           <t>Colouring visibly changes and produces a coherent image (no all-black, all-white, or uniform flat frame).</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="8" t="inlineStr"/>
-      <c r="G59" s="9" t="inlineStr"/>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: colour methods are all different</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
@@ -2059,9 +2449,14 @@
           <t>Colouring visibly changes and produces a coherent image (no all-black, all-white, or uniform flat frame).</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr"/>
-      <c r="F60" s="8" t="inlineStr"/>
-      <c r="G60" s="9" t="inlineStr"/>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: colour methods are all different</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
@@ -2082,9 +2477,14 @@
           <t>Colouring visibly changes and produces a coherent image (no all-black, all-white, or uniform flat frame).</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="8" t="inlineStr"/>
-      <c r="G61" s="9" t="inlineStr"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: colour methods are all different</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
@@ -2105,9 +2505,14 @@
           <t>Each palette applies immediately and looks distinct from the others.</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr"/>
-      <c r="G62" s="9" t="inlineStr"/>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: palettes are all different and coherent</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
@@ -2128,9 +2533,14 @@
           <t>Band frequency changes smoothly and live. No flicker, no stuck frame.</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="8" t="inlineStr"/>
-      <c r="G63" s="9" t="inlineStr"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: control changes the image</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
@@ -2151,9 +2561,14 @@
           <t>Colours shift phase smoothly through the palette.</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="8" t="inlineStr"/>
-      <c r="G64" s="9" t="inlineStr"/>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: control changes the image</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr"/>
+      <c r="G64" s="8" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
@@ -2166,17 +2581,22 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Toggle 'Log color scale'.</t>
+          <t>With 'Normalize deep colors' ON, toggle 'Log color scale'.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Colour distribution changes noticeably; image stays coherent.</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="8" t="inlineStr"/>
-      <c r="G65" s="9" t="inlineStr"/>
+          <t>Colour distribution changes noticeably; image stays coherent. (Log scale acts on the NORMALIZED mapping - with normalization off it has no visible effect.)</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: log-scale-changes-the-image</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr"/>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
@@ -2197,9 +2617,15 @@
           <t>Editor opens, the edit is reflected in the live image, and the dialog closes cleanly.</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr"/>
-      <c r="G66" s="9" t="inlineStr"/>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: gradient-edit-changes-the-image
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr"/>
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
@@ -2220,9 +2646,15 @@
           <t>Palette animates smoothly at the set speed and stops cleanly when disabled.</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr"/>
-      <c r="G67" s="9" t="inlineStr"/>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: palette_animation_advances_and_stops
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
@@ -2243,9 +2675,14 @@
           <t>Each visibly changes the rendering and can be turned back off.</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr"/>
-      <c r="G68" s="9" t="inlineStr"/>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: control changes the image</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
@@ -2266,9 +2703,15 @@
           <t>Relief shading appears and the highlight direction follows the angle.</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr"/>
-      <c r="F69" s="8" t="inlineStr"/>
-      <c r="G69" s="9" t="inlineStr"/>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: control changes the image
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
@@ -2289,9 +2732,15 @@
           <t>Glow appears around structure edges and responds to the controls.</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="8" t="inlineStr"/>
-      <c r="G70" s="9" t="inlineStr"/>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: control changes the image
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -2304,7 +2753,8 @@
       <c r="D71" s="6" t="n"/>
       <c r="E71" s="6" t="n"/>
       <c r="F71" s="6" t="n"/>
-      <c r="G71" s="7" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
@@ -2325,9 +2775,15 @@
           <t>Image visibly loses detail / gains flat interior - i.e. the control takes effect.</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="8" t="inlineStr"/>
-      <c r="G72" s="9" t="inlineStr"/>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: explicit iteration count honoured verbatim
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr"/>
+      <c r="H72" s="9" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
@@ -2348,9 +2804,15 @@
           <t>Detail returns. Render takes longer but completes; app stays responsive.</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr"/>
-      <c r="F73" s="8" t="inlineStr"/>
-      <c r="G73" s="9" t="inlineStr"/>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: explicit iteration count honoured verbatim
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
@@ -2371,9 +2833,14 @@
           <t>Iteration count in the status bar starts tracking zoom depth again.</t>
         </is>
       </c>
-      <c r="E74" s="9" t="inlineStr"/>
-      <c r="F74" s="8" t="inlineStr"/>
-      <c r="G74" s="9" t="inlineStr"/>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: recommended_max_iter_never_decreases_with_depth</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
@@ -2394,9 +2861,14 @@
           <t>Higher AA visibly smooths edges. Frame time increases accordingly in the Performance panel.</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr"/>
-      <c r="F75" s="8" t="inlineStr"/>
-      <c r="G75" s="9" t="inlineStr"/>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: supersampling softens edges</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
@@ -2417,9 +2889,15 @@
           <t>FPS, frame time, GPU time, mode, effective iterations, precision and orbit length all update and look plausible.</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr"/>
-      <c r="F76" s="8" t="inlineStr"/>
-      <c r="G76" s="9" t="inlineStr"/>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: perf-fields-populated
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -2432,7 +2910,8 @@
       <c r="D77" s="6" t="n"/>
       <c r="E77" s="6" t="n"/>
       <c r="F77" s="6" t="n"/>
-      <c r="G77" s="7" t="n"/>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
@@ -2453,9 +2932,14 @@
           <t>Dialog accepts full-precision input and the view jumps exactly there (status bar matches).</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr"/>
-      <c r="G78" s="9" t="inlineStr"/>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: go_to_round_trips_a_deep_coordinate</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr"/>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
@@ -2476,9 +2960,14 @@
           <t>Each jump lands somewhere valid and renders real structure - not a blank or all-interior frame.</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="8" t="inlineStr"/>
-      <c r="G79" s="9" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: random-locations-coherent</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -2499,9 +2988,14 @@
           <t>Bookmark is saved with a usable name and restores the exact view.</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="8" t="inlineStr"/>
-      <c r="G80" s="9" t="inlineStr"/>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: bookmark_round_trip</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
@@ -2514,17 +3008,22 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Bookmarks &gt; Manage… - rename and delete a bookmark.</t>
+          <t>Navigate &gt; Bookmarks… - delete a bookmark, including one you have just added.</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Manager opens, edits apply, deletion works, list stays consistent.</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="9" t="inlineStr"/>
+          <t>Dialog opens, deletion works, the remaining list and its thumbnails stay consistent. (There is no rename: a bookmark is named when it is added.)</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: bookmark_delete_keeps_the_list_consistent</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
@@ -2545,9 +3044,14 @@
           <t>Produces a shareable string/link for the current view without error.</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="8" t="inlineStr"/>
-      <c r="G82" s="9" t="inlineStr"/>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: share_string_round_trip</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
@@ -2568,9 +3072,14 @@
           <t>Import succeeds and the view lands at the imported coordinates.</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr"/>
-      <c r="F83" s="8" t="inlineStr"/>
-      <c r="G83" s="9" t="inlineStr"/>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: kfr_import_keeps_every_digit_of_a_deep_centre</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
@@ -2591,9 +3100,14 @@
           <t>The stored view is recovered and rendered.</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="9" t="inlineStr"/>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: metadata round-trips a deep view</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr"/>
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="9" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
@@ -2614,9 +3128,15 @@
           <t>Gallery opens, thumbnails display, and selecting one loads that view.</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr"/>
-      <c r="F85" s="8" t="inlineStr"/>
-      <c r="G85" s="9" t="inlineStr"/>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: gallery_scan_and_load
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -2629,7 +3149,8 @@
       <c r="D86" s="6" t="n"/>
       <c r="E86" s="6" t="n"/>
       <c r="F86" s="6" t="n"/>
-      <c r="G86" s="7" t="n"/>
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
@@ -2650,9 +3171,15 @@
           <t>An image is written without freezing the UI, and the app reports where it went.</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr"/>
-      <c r="F87" s="8" t="inlineStr"/>
-      <c r="G87" s="9" t="inlineStr"/>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: snapshot_writes_a_file
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
@@ -2673,9 +3200,14 @@
           <t>It matches what was on screen (same framing and colours) and is not corrupt or truncated.</t>
         </is>
       </c>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="8" t="inlineStr"/>
-      <c r="G88" s="9" t="inlineStr"/>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: snapshot-matches-the-view</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
@@ -2696,9 +3228,14 @@
           <t>Progress is shown, the export completes, and the app stays responsive or clearly indicates it is working.</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr"/>
-      <c r="F89" s="8" t="inlineStr"/>
-      <c r="G89" s="9" t="inlineStr"/>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: export-4k-complete</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
@@ -2719,9 +3256,14 @@
           <t>Full resolution, complete image, no missing tiles, no seams between tiles, no colour banding differences across tile boundaries.</t>
         </is>
       </c>
-      <c r="E90" s="9" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="9" t="inlineStr"/>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: tiled chunked export is bit-identical</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="9" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
@@ -2742,9 +3284,15 @@
           <t>Completes and matches the on-screen framing and colouring.</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr"/>
-      <c r="F91" s="8" t="inlineStr"/>
-      <c r="G91" s="9" t="inlineStr"/>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: deep-export-matches-the-view
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -2757,7 +3305,8 @@
       <c r="D92" s="6" t="n"/>
       <c r="E92" s="6" t="n"/>
       <c r="F92" s="6" t="n"/>
-      <c r="G92" s="7" t="n"/>
+      <c r="G92" s="6" t="n"/>
+      <c r="H92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
@@ -2778,9 +3327,15 @@
           <t>The app locates a minibrot and animates to it, landing on a real structure.</t>
         </is>
       </c>
-      <c r="E93" s="9" t="inlineStr"/>
-      <c r="F93" s="8" t="inlineStr"/>
-      <c r="G93" s="9" t="inlineStr"/>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: deep minibrot: size, framing, center accuracy
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr"/>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
@@ -2801,9 +3356,14 @@
           <t>Solver dialog opens, runs, and reports a result without hanging.</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr"/>
-      <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr"/>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: Misiurewicz multiplier vs closed forms</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
@@ -2824,9 +3384,14 @@
           <t>Camera moves smoothly through the script, frames resolve, captions (if any) display correctly.</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="8" t="inlineStr"/>
-      <c r="G95" s="9" t="inlineStr"/>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --livetest</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
@@ -2847,9 +3412,14 @@
           <t>Playback stops and normal interactive control returns.</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr"/>
-      <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="9" t="inlineStr"/>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: stopping_playback_restores_interaction</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
@@ -2870,9 +3440,14 @@
           <t>Creates a tour seeded at the current view without error.</t>
         </is>
       </c>
-      <c r="E97" s="9" t="inlineStr"/>
-      <c r="F97" s="8" t="inlineStr"/>
-      <c r="G97" s="9" t="inlineStr"/>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: generated dive script round-trips</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
@@ -2893,9 +3468,14 @@
           <t>Benchmark runs to completion and reports results; app remains usable afterwards.</t>
         </is>
       </c>
-      <c r="E98" s="9" t="inlineStr"/>
-      <c r="F98" s="8" t="inlineStr"/>
-      <c r="G98" s="9" t="inlineStr"/>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --benchmark-std</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr"/>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -2908,7 +3488,8 @@
       <c r="D99" s="6" t="n"/>
       <c r="E99" s="6" t="n"/>
       <c r="F99" s="6" t="n"/>
-      <c r="G99" s="7" t="n"/>
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
@@ -2929,9 +3510,15 @@
           <t>Help window opens, content is readable and scrolls, no broken layout or missing sections.</t>
         </is>
       </c>
-      <c r="E100" s="9" t="inlineStr"/>
-      <c r="F100" s="8" t="inlineStr"/>
-      <c r="G100" s="9" t="inlineStr"/>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: help_sections_all_render
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
@@ -2952,9 +3539,14 @@
           <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location), including a 'Deep-zoom arithmetic' line naming the backend in use.</t>
         </is>
       </c>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="8" t="inlineStr"/>
-      <c r="G101" s="9" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: diagnostics-populated</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
@@ -2975,9 +3567,14 @@
           <t>Names the arithmetic that has actually run and what the build contains. On the standard build: astro-float. On the accelerated build: rug, with the MPFR/GMP versions. Before any deep render it may say none has run yet - that is correct, not a missing value.</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr"/>
-      <c r="F102" s="8" t="inlineStr"/>
-      <c r="G102" s="9" t="inlineStr"/>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
@@ -2998,9 +3595,14 @@
           <t>On the STANDARD build: explains the optional accelerated download and offers two buttons. 'Download for this version' opens a URL containing THIS version's tag; 'All releases' opens the releases page. On the ACCELERATED build: says you are already running it instead, and offers no download.</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr"/>
-      <c r="F103" s="8" t="inlineStr"/>
-      <c r="G103" s="9" t="inlineStr"/>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: accelerated_asset_url</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
@@ -3021,9 +3623,14 @@
           <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr"/>
-      <c r="F104" s="8" t="inlineStr"/>
-      <c r="G104" s="9" t="inlineStr"/>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: issue_url_is_well_formed</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
@@ -3044,9 +3651,14 @@
           <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
         </is>
       </c>
-      <c r="E105" s="9" t="inlineStr"/>
-      <c r="F105" s="8" t="inlineStr"/>
-      <c r="G105" s="9" t="inlineStr"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: update_check_reaches_a_verdict</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
@@ -3067,9 +3679,14 @@
           <t>Setting persists and takes effect.</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr"/>
-      <c r="F106" s="8" t="inlineStr"/>
-      <c r="G106" s="9" t="inlineStr"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: a_setting_survives_save_and_reload</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -3082,7 +3699,8 @@
       <c r="D107" s="6" t="n"/>
       <c r="E107" s="6" t="n"/>
       <c r="F107" s="6" t="n"/>
-      <c r="G107" s="7" t="n"/>
+      <c r="G107" s="6" t="n"/>
+      <c r="H107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
@@ -3103,9 +3721,14 @@
           <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr"/>
-      <c r="F108" s="8" t="inlineStr"/>
-      <c r="G108" s="9" t="inlineStr"/>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — script: scripts/build-accelerated.ps1</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
@@ -3126,9 +3749,14 @@
           <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
         </is>
       </c>
-      <c r="E109" s="9" t="inlineStr"/>
-      <c r="F109" s="8" t="inlineStr"/>
-      <c r="G109" s="9" t="inlineStr"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
@@ -3149,9 +3777,14 @@
           <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr"/>
-      <c r="F110" s="8" t="inlineStr"/>
-      <c r="G110" s="9" t="inlineStr"/>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
@@ -3172,9 +3805,15 @@
           <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
         </is>
       </c>
-      <c r="E111" s="9" t="inlineStr"/>
-      <c r="F111" s="8" t="inlineStr"/>
-      <c r="G111" s="9" t="inlineStr"/>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr"/>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
@@ -3195,9 +3834,14 @@
           <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
         </is>
       </c>
-      <c r="E112" s="9" t="inlineStr"/>
-      <c r="F112" s="8" t="inlineStr"/>
-      <c r="G112" s="9" t="inlineStr"/>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --bench-bignum</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
@@ -3218,9 +3862,14 @@
           <t>Fails to start with a missing-DLL error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
         </is>
       </c>
-      <c r="E113" s="9" t="inlineStr"/>
-      <c r="F113" s="8" t="inlineStr"/>
-      <c r="G113" s="9" t="inlineStr"/>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr"/>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -3233,7 +3882,8 @@
       <c r="D114" s="6" t="n"/>
       <c r="E114" s="6" t="n"/>
       <c r="F114" s="6" t="n"/>
-      <c r="G114" s="7" t="n"/>
+      <c r="G114" s="6" t="n"/>
+      <c r="H114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
@@ -3254,9 +3904,15 @@
           <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
         </is>
       </c>
-      <c r="E115" s="9" t="inlineStr"/>
-      <c r="F115" s="8" t="inlineStr"/>
-      <c r="G115" s="9" t="inlineStr"/>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: clean-exit-marker
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
@@ -3277,9 +3933,14 @@
           <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr"/>
-      <c r="F116" s="8" t="inlineStr"/>
-      <c r="G116" s="9" t="inlineStr"/>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr"/>
+      <c r="G116" s="8" t="inlineStr"/>
+      <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
@@ -3300,9 +3961,14 @@
           <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
         </is>
       </c>
-      <c r="E117" s="9" t="inlineStr"/>
-      <c r="F117" s="8" t="inlineStr"/>
-      <c r="G117" s="9" t="inlineStr"/>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: no-crash-files</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -3315,7 +3981,8 @@
       <c r="D118" s="6" t="n"/>
       <c r="E118" s="6" t="n"/>
       <c r="F118" s="6" t="n"/>
-      <c r="G118" s="7" t="n"/>
+      <c r="G118" s="6" t="n"/>
+      <c r="H118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
@@ -3336,9 +4003,14 @@
           <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
         </is>
       </c>
-      <c r="E119" s="9" t="inlineStr"/>
-      <c r="F119" s="8" t="inlineStr"/>
-      <c r="G119" s="9" t="inlineStr"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --soak</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
@@ -3359,9 +4031,14 @@
           <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr"/>
-      <c r="F120" s="8" t="inlineStr"/>
-      <c r="G120" s="9" t="inlineStr"/>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --torture</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr"/>
+      <c r="G120" s="8" t="inlineStr"/>
+      <c r="H120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="n">
@@ -3382,9 +4059,15 @@
           <t>No crash and no stuck frame; the final selection is what renders.</t>
         </is>
       </c>
-      <c r="E121" s="9" t="inlineStr"/>
-      <c r="F121" s="8" t="inlineStr"/>
-      <c r="G121" s="9" t="inlineStr"/>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -3397,7 +4080,8 @@
       <c r="D122" s="6" t="n"/>
       <c r="E122" s="6" t="n"/>
       <c r="F122" s="6" t="n"/>
-      <c r="G122" s="7" t="n"/>
+      <c r="G122" s="6" t="n"/>
+      <c r="H122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
@@ -3418,32 +4102,37 @@
           <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
         </is>
       </c>
-      <c r="E123" s="9" t="inlineStr"/>
-      <c r="F123" s="8" t="inlineStr"/>
-      <c r="G123" s="9" t="inlineStr"/>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr"/>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G123"/>
+  <autoFilter ref="A1:H123"/>
   <mergeCells count="16">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A118:G118"/>
-    <mergeCell ref="A122:G122"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A114:G114"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A92:G92"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A107:G107"/>
-    <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A114:H114"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A107:H107"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A118:H118"/>
+    <mergeCell ref="A122:H122"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="G2:G123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -772,7 +772,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>70 of 106 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
+          <t>75 of 114 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
         </is>
       </c>
     </row>
@@ -786,14 +786,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>32 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
+          <t>33 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3 need a person outright, and 1 is a process step.</t>
+          <t>4 need a person outright, and 2 is a process step.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2952,17 +2952,17 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Random location, several times.</t>
+          <t>In the same dialog, enter an EXPRESSION rather than a decimal: put '-0.5 + 0.25*cos(pi/4)' in the real field and 'sqrt(2)/4' in the imaginary one, and go. Then try three that must be REFUSED: '2^i', 'sin(i)', and 'bogus(1)'.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Each jump lands somewhere valid and renders real structure - not a blank or all-interior frame.</t>
+          <t>The valid expressions evaluate and the view lands there; the coordinate readout shows the evaluated decimal, not the text you typed. Each invalid one is rejected with a visible message and the view does NOT move - a coordinate must never be silently half-read.</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: random-locations-coherent</t>
+          <t>AUTO — --selftest: expression functions &amp; constants</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -2980,17 +2980,17 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Bookmarks &gt; Add current view, then navigate away, then restore it from the menu.</t>
+          <t>Navigate &gt; Misiurewicz explorer… - let the gallery populate.</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Bookmark is saved with a usable name and restores the exact view.</t>
+          <t>A grid of Misiurewicz points appears, each with a live-rendered thumbnail that resolves (no permanently blank tiles) and its multiplier readouts: octaves of zoom per repeat and degrees of twist.</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: bookmark_round_trip</t>
+          <t>AUTO — --uitest: misiurewicz-explorer</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -3008,17 +3008,17 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Bookmarks… - delete a bookmark, including one you have just added.</t>
+          <t>In the explorer, pick a point and use it to jump (select, then solve and go).</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Dialog opens, deletion works, the remaining list and its thumbnails stay consistent. (There is no rename: a bookmark is named when it is added.)</t>
+          <t>The solve reports progress rather than freezing the window, and the view lands on that point at depth - the landed view shows the expected shape, not a blank or interior-filled frame.</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: bookmark_delete_keeps_the_list_consistent</t>
+          <t>AUTO — --uitest: misiurewicz-jump-lands</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr"/>
@@ -3036,17 +3036,17 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Share location… and copy the result.</t>
+          <t>Navigate &gt; Random location, several times.</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Produces a shareable string/link for the current view without error.</t>
+          <t>Each jump lands somewhere valid and renders real structure - not a blank or all-interior frame.</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: share_string_round_trip</t>
+          <t>AUTO — --selftest: random-locations-coherent</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -3064,17 +3064,17 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Import .kfr… with a Kalles Fraktaler / Fraktaler-3 parameter file.</t>
+          <t>Navigate &gt; Bookmarks &gt; Add current view, then navigate away, then restore it from the menu.</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Import succeeds and the view lands at the imported coordinates.</t>
+          <t>Bookmark is saved with a usable name and restores the exact view.</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: kfr_import_keeps_every_digit_of_a_deep_centre</t>
+          <t>AUTO — cargo test: bookmark_round_trip</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr"/>
@@ -3092,17 +3092,17 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Open view or location… with a previously exported PNG (or .fdn).</t>
+          <t>Navigate &gt; Bookmarks… - delete a bookmark, including one you have just added.</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>The stored view is recovered and rendered.</t>
+          <t>Dialog opens, deletion works, the remaining list and its thumbnails stay consistent. (There is no rename: a bookmark is named when it is added.)</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: metadata round-trips a deep view</t>
+          <t>AUTO — cargo test: bookmark_delete_keeps_the_list_consistent</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr"/>
@@ -3120,18 +3120,17 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Gallery… - browse and open an entry.</t>
+          <t>Navigate &gt; Share location… and copy the result.</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Gallery opens, thumbnails display, and selecting one loads that view.</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: gallery_scan_and_load
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Produces a shareable string/link for the current view without error.</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: share_string_round_trip</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -3139,42 +3138,55 @@
       <c r="H85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Export &amp; capture</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="7" t="n"/>
+      <c r="A86" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>Locations</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Navigate &gt; Import .kfr… with a Kalles Fraktaler / Fraktaler-3 parameter file.</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Import succeeds and the view lands at the imported coordinates.</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: kfr_import_keeps_every_digit_of_a_deep_centre</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="9" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Press Ctrl+S (Snapshot) at an interesting view.</t>
+          <t>File &gt; Open view or location… with a previously exported PNG (or .fdn).</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>An image is written without freezing the UI, and the app reports where it went.</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: snapshot_writes_a_file
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>The stored view is recovered and rendered.</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: metadata round-trips a deep view</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr"/>
@@ -3183,26 +3195,27 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Open the saved snapshot in an image viewer.</t>
+          <t>File &gt; Gallery… - browse and open an entry.</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>It matches what was on screen (same framing and colours) and is not corrupt or truncated.</t>
-        </is>
-      </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: snapshot-matches-the-view</t>
+          <t>Gallery opens, thumbnails display, and selecting one loads that view.</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: gallery_scan_and_load
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr"/>
@@ -3210,32 +3223,18 @@
       <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>Export &amp; capture</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>File &gt; Export image… at a LARGER size than the window (e.g. 4K) with supersampling on.</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>Progress is shown, the export completes, and the app stays responsive or clearly indicates it is working.</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: export-4k-complete</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr"/>
-      <c r="G89" s="8" t="inlineStr"/>
-      <c r="H89" s="9" t="inlineStr"/>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
@@ -3248,17 +3247,18 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Open the 4K export.</t>
+          <t>Press Ctrl+S (Snapshot) at an interesting view.</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Full resolution, complete image, no missing tiles, no seams between tiles, no colour banding differences across tile boundaries.</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: tiled chunked export is bit-identical</t>
+          <t>An image is written without freezing the UI, and the app reports where it went.</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: snapshot_writes_a_file
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr"/>
@@ -3276,18 +3276,17 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Export once at a DEEP view (1e30x or deeper).</t>
+          <t>Open the saved snapshot in an image viewer.</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Completes and matches the on-screen framing and colouring.</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: deep-export-matches-the-view
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>It matches what was on screen (same framing and colours) and is not corrupt or truncated.</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: snapshot-matches-the-view</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -3295,42 +3294,55 @@
       <c r="H91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="7" t="n"/>
+      <c r="A92" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Export &amp; capture</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>File &gt; Export image… at a LARGER size than the window (e.g. 4K) with supersampling on.</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>Progress is shown, the export completes, and the app stays responsive or clearly indicates it is working.</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: export-4k-complete</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="9" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Press M (Tools &gt; Find minibrot + zoom to it).</t>
+          <t>Open the 4K export.</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>The app locates a minibrot and animates to it, landing on a real structure.</t>
-        </is>
-      </c>
-      <c r="E93" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: deep minibrot: size, framing, center accuracy
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Full resolution, complete image, no missing tiles, no seams between tiles, no colour banding differences across tile boundaries.</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: tiled chunked export is bit-identical</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -3339,26 +3351,27 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tools &gt; Newton / Misiurewicz solver… - run it on the current view.</t>
+          <t>Export once at a DEEP view (1e30x or deeper).</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Solver dialog opens, runs, and reports a result without hanging.</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: Misiurewicz multiplier vs closed forms</t>
+          <t>Completes and matches the on-screen framing and colouring.</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: deep-export-matches-the-view
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
@@ -3366,32 +3379,18 @@
       <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>Tools &gt; Play tour… and play a bundled tour for at least a minute.</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>Camera moves smoothly through the script, frames resolve, captions (if any) display correctly.</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --livetest</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr"/>
-      <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="n"/>
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
@@ -3404,17 +3403,18 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Close the tour player.</t>
+          <t>Press M (Tools &gt; Find minibrot + zoom to it).</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Playback stops and normal interactive control returns.</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: stopping_playback_restores_interaction</t>
+          <t>The app locates a minibrot and animates to it, landing on a real structure.</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: deep minibrot: size, framing, center accuracy
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
@@ -3432,17 +3432,17 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tools &gt; Tour from current view… </t>
+          <t>Tools &gt; Newton / Misiurewicz solver… - run it on the current view.</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Creates a tour seeded at the current view without error.</t>
+          <t>Solver dialog opens, runs, and reports a result without hanging.</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: generated dive script round-trips</t>
+          <t>AUTO — --selftest: Misiurewicz multiplier vs closed forms</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -3460,17 +3460,17 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tools &gt; Benchmark… and let it finish.</t>
+          <t>Tools &gt; Play tour… and play a bundled tour for at least a minute.</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Benchmark runs to completion and reports results; app remains usable afterwards.</t>
+          <t>Camera moves smoothly through the script, frames resolve, captions (if any) display correctly.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --benchmark-std</t>
+          <t>AUTO — CLI: --livetest</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -3478,42 +3478,55 @@
       <c r="H98" s="9" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Help &amp; settings</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="7" t="n"/>
+      <c r="A99" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>Close the tour player.</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>Playback stops and normal interactive control returns.</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: stopping_playback_restores_interaction</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr"/>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Press F1 (Help &amp; reference).</t>
+          <t xml:space="preserve">Tools &gt; Tour from current view… </t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Help window opens, content is readable and scrolls, no broken layout or missing sections.</t>
-        </is>
-      </c>
-      <c r="E100" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: help_sections_all_render
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Creates a tour seeded at the current view without error.</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: generated dive script round-trips</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -3522,26 +3535,26 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Diagnostics… </t>
+          <t>Tools &gt; Benchmark… and let it finish.</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location), including a 'Deep-zoom arithmetic' line naming the backend in use.</t>
+          <t>Benchmark runs to completion and reports results; app remains usable afterwards.</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --uitest: diagnostics-populated</t>
+          <t>AUTO — CLI: --benchmark-std</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -3549,32 +3562,18 @@
       <c r="H101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>Help &amp; settings</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>Help &gt; About (the last Help section). Read the 'Deep-zoom arithmetic' line.</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>Names the arithmetic that has actually run and what the build contains. On the standard build: astro-float. On the accelerated build: rug, with the MPFR/GMP versions. Before any deep render it may say none has run yet - that is correct, not a missing value.</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: about_names_the_running_backend</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr"/>
-      <c r="G102" s="8" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="6" t="n"/>
+      <c r="G102" s="6" t="n"/>
+      <c r="H102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
@@ -3587,17 +3586,18 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Faster deep zoom… </t>
+          <t>Press F1 (Help &amp; reference).</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>On the STANDARD build: explains the optional accelerated download and offers two buttons. 'Download for this version' opens a URL containing THIS version's tag; 'All releases' opens the releases page. On the ACCELERATED build: says you are already running it instead, and offers no download.</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: accelerated_asset_url</t>
+          <t>Help window opens, content is readable and scrolls, no broken layout or missing sections.</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: help_sections_all_render
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -3615,17 +3615,17 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Report an issue… </t>
+          <t xml:space="preserve">Help &gt; Diagnostics… </t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
+          <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location), including a 'Deep-zoom arithmetic' line naming the backend in use.</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: issue_url_is_well_formed</t>
+          <t>AUTO — --uitest: diagnostics-populated</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -3643,17 +3643,17 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; Check for updates.</t>
+          <t>Help &gt; About (the last Help section). Read the 'Deep-zoom arithmetic' line.</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
+          <t>Names the arithmetic that has actually run and what the build contains. On the standard build: astro-float. On the accelerated build: rug, with the MPFR/GMP versions. Before any deep render it may say none has run yet - that is correct, not a missing value.</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: update_check_reaches_a_verdict</t>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Settings - change a setting, close and reopen the menu.</t>
+          <t xml:space="preserve">Help &gt; Faster deep zoom… </t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Setting persists and takes effect.</t>
+          <t>On the STANDARD build: explains the optional accelerated download and offers two buttons. 'Download for this version' opens a URL containing THIS version's tag; 'All releases' opens the releases page. On the ACCELERATED build: says you are already running it instead, and offers no download.</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: a_setting_survives_save_and_reload</t>
+          <t>AUTO — cargo test: accelerated_asset_url</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -3689,41 +3689,55 @@
       <c r="H106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Accelerated build</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
-      <c r="G107" s="6" t="n"/>
-      <c r="H107" s="7" t="n"/>
+      <c r="A107" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Help &amp; settings</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Help &gt; Report an issue… </t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: issue_url_is_well_formed</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
+          <t>Help &gt; Check for updates.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
+          <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>AUTO — script: scripts/build-accelerated.ps1</t>
+          <t>AUTO — cargo test: update_check_reaches_a_verdict</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -3732,26 +3746,26 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; About on that build.</t>
+          <t>File &gt; Settings - change a setting, close and reopen the menu.</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
+          <t>Setting persists and takes effect.</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: about_names_the_running_backend</t>
+          <t>AUTO — cargo test: a_setting_survives_save_and_reload</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr"/>
@@ -3759,32 +3773,18 @@
       <c r="H109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>Accelerated build</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>Check that your existing locations, bookmarks and last session are present.</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="inlineStr"/>
-      <c r="G110" s="8" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr"/>
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="6" t="n"/>
+      <c r="G110" s="6" t="n"/>
+      <c r="H110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
@@ -3797,18 +3797,17 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
+          <t>WINDOWS: extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — script: scripts/build-accelerated.ps1</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -3826,17 +3825,17 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
+          <t>LINUX: extract fractadyne-&lt;tag&gt;-linux-x64-accelerated.tar.gz to a new folder on a distro with glibc 2.39+ (Ubuntu 24.04+, Debian 13+) and run ./fractadyne from it. Use a machine with only the RUNTIME libraries (libgmp10, libmpfr6) - no -dev packages, no build tools.</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
+          <t>Window opens normally. This package deliberately does NOT bundle GMP/MPFR, so it must find the system ones; a missing-library error here means the packaging assumed something the target does not have.</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --bench-bignum</t>
+          <t>AUTO — script: scripts/build-accelerated.sh</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -3854,12 +3853,12 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after.</t>
+          <t>LINUX: run the same tarball on an OLDER distro (Ubuntu 22.04 / Debian 12).</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Fails to start with a missing-DLL error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
+          <t>It refuses to start with a clear glibc / missing-symbol message - and the STANDARD linux-x64.tar.gz still runs there. The accelerated package has a higher floor by construction (its GMP requirement forces a newer build host); what must not happen is a confusing failure with no standard build to fall back to.</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
@@ -3872,42 +3871,55 @@
       <c r="H113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Persistence</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="7" t="n"/>
+      <c r="A114" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>On the accelerated build, open Help &gt; Faster deep zoom and read the download link it offers (hover it if the text is elided).</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>It names the package for the platform you are running - .zip on Windows, .tar.gz on Linux - and the version matches the running build. Offering the other platform's file is a dead download even though the link resolves.</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: the_url_names_this_platforms_package</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr"/>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+          <t>Help &gt; About on that build.</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --uitest: clean-exit-marker
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -3916,26 +3928,26 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Relaunch the app.</t>
+          <t>Check that your existing locations, bookmarks and last session are present.</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
+          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -3944,26 +3956,27 @@
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Check config\logs for crash-*.txt files created during this run.</t>
+          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --uitest: no-crash-files</t>
+          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -3971,41 +3984,55 @@
       <c r="H117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="7" t="n"/>
+      <c r="A118" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --bench-bignum</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+          <t>WINDOWS: delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after. (LINUX equivalent: temporarily move the tarball to a machine without libmpfr6.)</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --soak</t>
+          <t>Fails to start with a missing-library error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -4014,26 +4041,26 @@
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+          <t>On the PUBLISHED release page, compare the 'Which download?' table against the Assets list at the foot of the page.</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --torture</t>
+          <t>Every attached asset has a row, and every row names an attached asset. The table is written by hand and the asset list is produced by the build jobs, so they drift silently: v0.2.41-beta.20 shipped the Linux accelerated tarball attached but unlisted, which reads to a visitor exactly like a build that failed.</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -4041,98 +4068,296 @@
       <c r="H120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>No crash and no stuck frame; the final selection is what renders.</t>
-        </is>
-      </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="F121" s="6" t="n"/>
+      <c r="G121" s="6" t="n"/>
+      <c r="H121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: clean-exit-marker
 Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
-      <c r="F121" s="9" t="inlineStr"/>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="9" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Sign-off</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
-      <c r="G122" s="6" t="n"/>
-      <c r="H122" s="7" t="n"/>
+      <c r="F122" s="9" t="inlineStr"/>
+      <c r="G122" s="8" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Persistence</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+          <t>Relaunch the app.</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
       <c r="G123" s="8" t="inlineStr"/>
       <c r="H123" s="9" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Check config\logs for crash-*.txt files created during this run.</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: no-crash-files</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="E125" s="6" t="n"/>
+      <c r="F125" s="6" t="n"/>
+      <c r="G125" s="6" t="n"/>
+      <c r="H125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --soak</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="9" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>With the view fully settled and the mouse OFF the window, watch the performance panel's activity line and your GPU/fan (Task Manager's GPU column, or nvidia-smi / radeontop) for a minute.</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>The activity line reads 'idle' AND the app stops drawing: GPU usage falls to ~0 and STAYS there. A steady 1-4 fps trickle on a static picture is the defect fixed in beta.18 - the app was re-rendering a finished frame forever. Touch the window and it must wake instantly. FRACTADYNE_TRACE=idle names whatever is holding it awake if this fails.</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: both_views_quiet_and_nothing_animating_is_quiescent
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr"/>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --torture</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr"/>
+      <c r="G128" s="8" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>No crash and no stuck frame; the final selection is what renders.</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr"/>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="6" t="n"/>
+      <c r="F130" s="6" t="n"/>
+      <c r="G130" s="6" t="n"/>
+      <c r="H130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="n">
+        <v>114</v>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr"/>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H123"/>
+  <autoFilter ref="A1:H131"/>
   <mergeCells count="16">
-    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A130:H130"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="A77:H77"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A114:H114"/>
+    <mergeCell ref="A95:H95"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A107:H107"/>
-    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A125:H125"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A118:H118"/>
-    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A89:H89"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="G2:G131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -772,7 +772,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>75 of 114 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
+          <t>81 of 124 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
         </is>
       </c>
     </row>
@@ -786,14 +786,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
+          <t>34 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4 need a person outright, and 2 is a process step.</t>
+          <t>7 need a person outright, and 2 is a process step.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -912,7 +912,7 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Launch the release build with a CLEAN profile: rename %APPDATA%\Fractadyne\Fractadyne\config to config.bak first, so this is a true first run.</t>
+          <t>Launch the release build with a CLEAN profile: move the profile aside first, so this is a true first run. Windows: rename %APPDATA%\Fractadyne\Fractadyne\config to config.bak. Linux: move ~/.config/Fractadyne aside.</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -3775,7 +3775,7 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="B110" s="6" t="n"/>
@@ -3792,22 +3792,22 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>WINDOWS: extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
+          <t>Move ~/.config/Fractadyne aside (that is where `directories::ProjectDirs` puts the profile; $XDG_CONFIG_HOME overrides it) and launch the extracted tarball's ./fractadyne.</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
+          <t>True first run: welcome dialog, home view, no console errors. On exit a new ~/.config/Fractadyne/session.toml exists — state belongs in the user profile, never beside the binary, so an extracted folder stays disposable.</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>AUTO — script: scripts/build-accelerated.ps1</t>
+          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -3820,22 +3820,22 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>LINUX: extract fractadyne-&lt;tag&gt;-linux-x64-accelerated.tar.gz to a new folder on a distro with glibc 2.39+ (Ubuntu 24.04+, Debian 13+) and run ./fractadyne from it. Use a machine with only the RUNTIME libraries (libgmp10, libmpfr6) - no -dev packages, no build tools.</t>
+          <t>From the extracted tarball run ./fractadyne --selftest and read the goldens section.</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Window opens normally. This package deliberately does NOT bundle GMP/MPFR, so it must find the system ones; a missing-library error here means the packaging assumed something the target does not have.</t>
+          <t>It runs to a verdict. Goldens are compared with the CROSS-GPU tolerance, not the strict one, because validation/golden/BLESSED-GPU.txt ships in the tarball — if the run reports strict failures on a non-3080 card, that file is missing from the package and every Linux tester will see expected vendor variance as a failure.</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>AUTO — script: scripts/build-accelerated.sh</t>
+          <t>AUTO — CLI: --selftest</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -3848,22 +3848,22 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>LINUX: run the same tarball on an OLDER distro (Ubuntu 22.04 / Debian 12).</t>
+          <t>Run ./fractadyne --selftest --selftest-filter live-res, then read the adapter line in the log: 'capability: TIMESTAMP_QUERY=true|false'.</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>It refuses to start with a clear glibc / missing-symbol message - and the STANDARD linux-x64.tar.gz still runs there. The accelerated package has a higher floor by construction (its GMP requirement forces a newer build host); what must not happen is a confusing failure with no standard build to fall back to.</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+          <t>The settled-resolution invariant passes WHATEVER that capability says. This is the point of running it here: TIMESTAMP_QUERY is genuinely absent on the GL backend and on several Mesa/RADV/ANV combinations, and until now that path had only ever been faked on an NVIDIA card with FRACTADYNE_NO_TIMESTAMPS=1. A view stuck at ~1/3 resolution forever is the failure.</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: live-res</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
@@ -3876,22 +3876,22 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>On the accelerated build, open Help &gt; Faster deep zoom and read the download link it offers (hover it if the text is elided).</t>
+          <t>Repeat the launch on each GPU the rig can take (NVIDIA / AMD / Intel), recording for each: the adapter line, the chosen backend, and whether deep views render correctly.</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>It names the package for the platform you are running - .zip on Windows, .tar.gz on Linux - and the version matches the running build. Offering the other platform's file is a dead download even though the link resolves.</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: the_url_names_this_platforms_package</t>
+          <t>Every card opens a window and renders. Record the adapter + backend per card — cross-vendor differences in the deep floatexp path are a known open bug (3080 all-black vs 3070 rich), so this is evidence-gathering as much as pass/fail.</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -3904,22 +3904,22 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; About on that build.</t>
+          <t>Run once under Wayland and once under X11 (log into an X11 session, or unset WAYLAND_DISPLAY so winit falls back).</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: about_names_the_running_backend</t>
+          <t>Window opens, resizes, and scales sensibly under both. Note any difference in DPI handling, cursor behaviour or window decorations.</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -3932,22 +3932,22 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Check that your existing locations, bookmarks and last session are present.</t>
+          <t>Help &gt; Diagnostics — check the four readings that have platform-specific implementations: process memory (/proc/self/status), free disk (statvfs), CPU topology (/proc/cpuinfo), and GPU VRAM (amdgpu sysfs, else nvidia-smi).</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
+          <t>All four report PLAUSIBLE, non-zero values that match what the system tools say. These were written for Linux and verified only to compile, so a zero or an absurd figure here is a real defect, not a cosmetic one.</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
+          <t>AUTO — --uitest: diagnostics-populated</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -3960,23 +3960,22 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
+          <t>Exercise the native file dialogs: File &gt; Open view or location…, and an export that asks for a path.</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>The GTK dialogs open, are navigable, and the chosen path is honoured. A missing GTK runtime shows up here first.</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr"/>
@@ -3989,22 +3988,22 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
+          <t>Run on a box with no audio server (or with FRACTADYNE_NO_SOUND=1) and let a long render finish.</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
+          <t>No crash, no hang, and no error spew when the finish tone cannot play — audio is a nicety and must never be able to take the app down.</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --bench-bignum</t>
+          <t>AUTO — CLI: --no-sound</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -4017,22 +4016,23 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>WINDOWS: delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after. (LINUX equivalent: temporarily move the tarball to a machine without libmpfr6.)</t>
+          <t>Run ./fractadyne --version over SSH with no DISPLAY set.</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Fails to start with a missing-library error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+          <t>Prints 'fractadyne &lt;version&gt; (build N)' and exits cleanly without trying to open a window. The version must match the tag being reviewed.</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: title_string_matches_version
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -4045,22 +4045,22 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>On the PUBLISHED release page, compare the 'Which download?' table against the Assets list at the foot of the page.</t>
+          <t>After the session above, check ~/.config/Fractadyne/logs/ for crash-*.txt.</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Every attached asset has a row, and every row names an attached asset. The table is written by hand and the asset list is produced by the build jobs, so they drift silently: v0.2.41-beta.20 shipped the Linux accelerated tarball attached but unlisted, which reads to a visitor exactly like a build that failed.</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>No new crash reports. (If any exist this run FAILS and the file must be attached — the log directory is the Linux equivalent of the Windows config\logs folder checked earlier.)</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: no-crash-files</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -4070,7 +4070,7 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="B121" s="6" t="n"/>
@@ -4087,23 +4087,22 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+          <t>WINDOWS: extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
-        </is>
-      </c>
-      <c r="E122" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --uitest: clean-exit-marker
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — script: scripts/build-accelerated.ps1</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -4116,22 +4115,22 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Relaunch the app.</t>
+          <t>LINUX: extract fractadyne-&lt;tag&gt;-linux-x64-accelerated.tar.gz to a new folder on a distro with glibc 2.39+ (Ubuntu 24.04+, Debian 13+) and run ./fractadyne from it. Use a machine with only the RUNTIME libraries (libgmp10, libmpfr6) - no -dev packages, no build tools.</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+          <t>Window opens normally. This package deliberately does NOT bundle GMP/MPFR, so it must find the system ones; a missing-library error here means the packaging assumed something the target does not have.</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
+          <t>AUTO — script: scripts/build-accelerated.sh</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -4144,22 +4143,22 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Check config\logs for crash-*.txt files created during this run.</t>
+          <t>LINUX: run the same tarball on an OLDER distro (Ubuntu 22.04 / Debian 12).</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
-        </is>
-      </c>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --uitest: no-crash-files</t>
+          <t>It refuses to start with a clear glibc / missing-symbol message - and the STANDARD linux-x64.tar.gz still runs there. The accelerated package has a higher floor by construction (its GMP requirement forces a newer build host); what must not happen is a confusing failure with no standard build to fall back to.</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -4167,41 +4166,55 @@
       <c r="H124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="6" t="n"/>
-      <c r="G125" s="6" t="n"/>
-      <c r="H125" s="7" t="n"/>
+      <c r="A125" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>On the accelerated build, open Help &gt; Faster deep zoom and read the download link it offers (hover it if the text is elided).</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>It names the package for the platform you are running - .zip on Windows, .tar.gz on Linux - and the version matches the running build. Offering the other platform's file is a dead download even though the link resolves.</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: the_url_names_this_platforms_package</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr"/>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+          <t>Help &gt; About on that build.</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
+          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --soak</t>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -4210,27 +4223,26 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>With the view fully settled and the mouse OFF the window, watch the performance panel's activity line and your GPU/fan (Task Manager's GPU column, or nvidia-smi / radeontop) for a minute.</t>
+          <t>Check that your existing locations, bookmarks and last session are present.</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>The activity line reads 'idle' AND the app stops drawing: GPU usage falls to ~0 and STAYS there. A steady 1-4 fps trickle on a static picture is the defect fixed in beta.18 - the app was re-rendering a finished frame forever. Touch the window and it must wake instantly. FRACTADYNE_TRACE=idle names whatever is holding it awake if this fails.</t>
-        </is>
-      </c>
-      <c r="E127" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: both_views_quiet_and_nothing_animating_is_quiescent
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -4239,26 +4251,27 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
-        </is>
-      </c>
-      <c r="E128" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --torture</t>
+          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr"/>
@@ -4267,27 +4280,26 @@
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>No crash and no stuck frame; the final selection is what renders.</t>
-        </is>
-      </c>
-      <c r="E129" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --bench-bignum</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -4295,36 +4307,50 @@
       <c r="H129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>Sign-off</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="n"/>
-      <c r="C130" s="6" t="n"/>
-      <c r="D130" s="6" t="n"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" s="6" t="n"/>
-      <c r="G130" s="6" t="n"/>
-      <c r="H130" s="7" t="n"/>
+      <c r="A130" s="8" t="n">
+        <v>115</v>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>WINDOWS: delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after. (LINUX equivalent: temporarily move the tarball to a machine without libmpfr6.)</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>Fails to start with a missing-library error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr"/>
+      <c r="G130" s="8" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+          <t>On the PUBLISHED release page, compare the 'Which download?' table against the Assets list at the foot of the page.</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
+          <t>Every attached asset has a row, and every row names an attached asset. The table is written by hand and the asset list is produced by the build jobs, so they drift silently: v0.2.41-beta.20 shipped the Linux accelerated tarball attached but unlisted, which reads to a visitor exactly like a build that failed.</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -4336,10 +4362,279 @@
       <c r="G131" s="8" t="inlineStr"/>
       <c r="H131" s="9" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="n"/>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="6" t="n"/>
+      <c r="E132" s="6" t="n"/>
+      <c r="F132" s="6" t="n"/>
+      <c r="G132" s="6" t="n"/>
+      <c r="H132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: clean-exit-marker
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr"/>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Relaunch the app.</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr"/>
+      <c r="G134" s="8" t="inlineStr"/>
+      <c r="H134" s="9" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Check the profile's logs folder for crash-*.txt files created during this run (Windows: %APPDATA%\Fractadyne\Fractadyne\config\logs; Linux: ~/.config/Fractadyne/logs).</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: no-crash-files</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="9" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="6" t="n"/>
+      <c r="F136" s="6" t="n"/>
+      <c r="G136" s="6" t="n"/>
+      <c r="H136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --soak</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr"/>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="9" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>With the view fully settled and the mouse OFF the window, watch the performance panel's activity line and your GPU/fan (Task Manager's GPU column, or nvidia-smi / radeontop) for a minute.</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>The activity line reads 'idle' AND the app stops drawing: GPU usage falls to ~0 and STAYS there. A steady 1-4 fps trickle on a static picture is the defect fixed in beta.18 - the app was re-rendering a finished frame forever. Touch the window and it must wake instantly. FRACTADYNE_TRACE=idle names whatever is holding it awake if this fails.</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: both_views_quiet_and_nothing_animating_is_quiescent
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr"/>
+      <c r="G138" s="8" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --torture</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr"/>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="9" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>No crash and no stuck frame; the final selection is what renders.</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr"/>
+      <c r="G140" s="8" t="inlineStr"/>
+      <c r="H140" s="9" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+      <c r="E141" s="6" t="n"/>
+      <c r="F141" s="6" t="n"/>
+      <c r="G141" s="6" t="n"/>
+      <c r="H141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>124</v>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr"/>
+      <c r="G142" s="8" t="inlineStr"/>
+      <c r="H142" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H131"/>
-  <mergeCells count="16">
-    <mergeCell ref="A130:H130"/>
+  <autoFilter ref="A1:H142"/>
+  <mergeCells count="17">
+    <mergeCell ref="A136:H136"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A55:H55"/>
@@ -4350,14 +4645,15 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A141:H141"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A132:H132"/>
     <mergeCell ref="A110:H110"/>
     <mergeCell ref="A89:H89"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="G2:G142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -772,7 +772,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>81 of 124 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
+          <t>81 of 131 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
         </is>
       </c>
     </row>
@@ -786,14 +786,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>34 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
+          <t>38 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7 need a person outright, and 2 is a process step.</t>
+          <t>10 need a person outright, and 2 is a process step.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2638,18 +2638,17 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Set Animate to on and watch for a few seconds, then set it back to Off.</t>
+          <t>In the gradient editor, compare the preview bar against the rendered image: pick a stop, note its colour in the bar, and find that colour in the fractal.</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Palette animates smoothly at the set speed and stops cleanly when disabled.</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: palette_animation_advances_and_stops
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>The preview bar shows the SAME colours the image is painted with - not lighter, not darker. (Before beta.23 the bar gamma-encoded its swatches, so every one read markedly lighter than the pixels it stood for. No machine check compares the two.)</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr"/>
@@ -2667,17 +2666,18 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>In Effects, toggle 'Binary (set)' and 'Duotone'.</t>
+          <t>In the gradient editor, click 'Import .map…' and load a Fractint or Kalles Fraktaler .map palette file (e.g. Fractint's default.map).</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Each visibly changes the rendering and can be turned back off.</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: control changes the image</t>
+          <t>The palette applies immediately as HARD BANDS - flat steps of colour, not a smooth ramp - and the message reports how many entries were read. For a Fractint file it also says the table is 6-bit VGA (white is 252, not 255).</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: map-bands-are-exact
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr"/>
@@ -2695,17 +2695,17 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>In Effects, enable '3D relief lighting' and drag the Light angle control.</t>
+          <t>With that .map still loaded, untick 'Hard bands (no blending between entries)'.</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Relief shading appears and the highlight direction follows the angle.</t>
+          <t>The same colours blend into a smooth gradient. Ticking it again restores the hard steps.</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>PARTLY AUTO — --selftest: control changes the image
+          <t>PARTLY AUTO — --selftest: map-bands-are-exact
 Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
@@ -2724,18 +2724,17 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>In Effects, enable 'Distance glow' and adjust its strength/width.</t>
+          <t>⭐Render a view through the imported .map, then render the SAME location and palette in Fractint (or Kalles Fraktaler) and compare the two side by side. Mark BLOCKED if that application is not available.</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Glow appears around structure edges and responds to the controls.</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: control changes the image
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>The band structure and the ORDER of colours match. This is the one claim no automated check can make: our checks prove the file's values reach the framebuffer unaltered, not that our iteration→palette-index mapping is the same as theirs. See design/palette-import.md §7.</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr"/>
@@ -2743,41 +2742,56 @@
       <c r="H70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="7" t="n"/>
+      <c r="A71" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Coloring</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Click 'Import .ugr…' and load an Ultra Fractal gradient file (these normally hold many gradients). Pick one from the list that appears.</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>A scrollable list appears, each row showing the gradient's name AND a preview swatch of it. Clicking a row applies that gradient immediately. Reds look red and blues look blue - the format stores colour with red in the LOW byte, so a mistake here swaps them while still looking like a plausible palette.</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: ugr-color-is-bgr
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Coloring</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>In Quality, toggle 'Auto-scale iterations with zoom' off and set Iterations manually to a low value (e.g. 200) at a moderately deep view.</t>
+          <t>Click 'Import .ggr…' and load a GIMP gradient, then read the note in the editor and press 'Convert to editable stops'.</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Image visibly loses detail / gains flat interior - i.e. the control takes effect.</t>
+          <t>The editor says how many segments were imported, and that they carry midpoints, blend curves and colour spaces. 'Convert to editable stops' warns that it DISCARDS those, and after it the per-stop rows appear.</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>PARTLY AUTO — --selftest: explicit iteration count honoured verbatim
+          <t>PARTLY AUTO — --selftest: ggr-colour-space-is-per-segment
 Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
@@ -2787,27 +2801,26 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Coloring</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Raise Iterations to a high value (e.g. 100000) at that same view.</t>
+          <t>⭐Click 'Import .ase…' and load a real Adobe swatch file.</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Detail returns. Render takes longer but completes; app stays responsive.</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: explicit iteration count honoured verbatim
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>It loads as an evenly spaced gradient, OR is rejected with a specific reason. Either outcome is information: this is the ONE importer written from the published format rather than against a real file, so the first real .ase is its actual test. A rejection is worth reporting, not working around.</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -2816,26 +2829,27 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Coloring</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Re-enable 'Auto-scale iterations with zoom'.</t>
+          <t>Set Animate to on and watch for a few seconds, then set it back to Off.</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Iteration count in the status bar starts tracking zoom depth again.</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: recommended_max_iter_never_decreases_with_depth</t>
+          <t>Palette animates smoothly at the set speed and stops cleanly when disabled.</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: palette_animation_advances_and_stops
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -2844,26 +2858,26 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Coloring</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Change Anti-alias between 1x and 2x (and higher if offered) and compare edges.</t>
+          <t>In Effects, toggle 'Binary (set)' and 'Duotone'.</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Higher AA visibly smooths edges. Frame time increases accordingly in the Performance panel.</t>
+          <t>Each visibly changes the rendering and can be turned back off.</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: supersampling softens edges</t>
+          <t>AUTO — --selftest: control changes the image</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -2872,26 +2886,26 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Coloring</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Open the Performance panel and watch it while navigating.</t>
+          <t>In Effects, enable '3D relief lighting' and drag the Light angle control.</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>FPS, frame time, GPU time, mode, effective iterations, precision and orbit length all update and look plausible.</t>
+          <t>Relief shading appears and the highlight direction follows the angle.</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>PARTLY AUTO — --uitest: perf-fields-populated
+          <t>PARTLY AUTO — --selftest: control changes the image
 Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
@@ -2900,69 +2914,71 @@
       <c r="H76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Locations</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="7" t="n"/>
+      <c r="A77" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Coloring</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>In Effects, enable 'Distance glow' and adjust its strength/width.</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Glow appears around structure edges and responds to the controls.</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: control changes the image
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>Locations</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>Navigate &gt; Go to location… and enter a known deep coordinate.</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>Dialog accepts full-precision input and the view jumps exactly there (status bar matches).</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: go_to_round_trips_a_deep_coordinate</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>In the same dialog, enter an EXPRESSION rather than a decimal: put '-0.5 + 0.25*cos(pi/4)' in the real field and 'sqrt(2)/4' in the imaginary one, and go. Then try three that must be REFUSED: '2^i', 'sin(i)', and 'bogus(1)'.</t>
+          <t>In Quality, toggle 'Auto-scale iterations with zoom' off and set Iterations manually to a low value (e.g. 200) at a moderately deep view.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>The valid expressions evaluate and the view lands there; the coordinate readout shows the evaluated decimal, not the text you typed. Each invalid one is rejected with a visible message and the view does NOT move - a coordinate must never be silently half-read.</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: expression functions &amp; constants</t>
+          <t>Image visibly loses detail / gains flat interior - i.e. the control takes effect.</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: explicit iteration count honoured verbatim
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -2971,26 +2987,27 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Misiurewicz explorer… - let the gallery populate.</t>
+          <t>Raise Iterations to a high value (e.g. 100000) at that same view.</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>A grid of Misiurewicz points appears, each with a live-rendered thumbnail that resolves (no permanently blank tiles) and its multiplier readouts: octaves of zoom per repeat and degrees of twist.</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --uitest: misiurewicz-explorer</t>
+          <t>Detail returns. Render takes longer but completes; app stays responsive.</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: explicit iteration count honoured verbatim
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -2999,26 +3016,26 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>In the explorer, pick a point and use it to jump (select, then solve and go).</t>
+          <t>Re-enable 'Auto-scale iterations with zoom'.</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>The solve reports progress rather than freezing the window, and the view lands on that point at depth - the landed view shows the expected shape, not a blank or interior-filled frame.</t>
+          <t>Iteration count in the status bar starts tracking zoom depth again.</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --uitest: misiurewicz-jump-lands</t>
+          <t>AUTO — cargo test: recommended_max_iter_never_decreases_with_depth</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr"/>
@@ -3027,26 +3044,26 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Random location, several times.</t>
+          <t>Change Anti-alias between 1x and 2x (and higher if offered) and compare edges.</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Each jump lands somewhere valid and renders real structure - not a blank or all-interior frame.</t>
+          <t>Higher AA visibly smooths edges. Frame time increases accordingly in the Performance panel.</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: random-locations-coherent</t>
+          <t>AUTO — --selftest: supersampling softens edges</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -3055,26 +3072,27 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Locations</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Bookmarks &gt; Add current view, then navigate away, then restore it from the menu.</t>
+          <t>Open the Performance panel and watch it while navigating.</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Bookmark is saved with a usable name and restores the exact view.</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: bookmark_round_trip</t>
+          <t>FPS, frame time, GPU time, mode, effective iterations, precision and orbit length all update and look plausible.</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --uitest: perf-fields-populated
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr"/>
@@ -3082,32 +3100,18 @@
       <c r="H83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Locations</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Navigate &gt; Bookmarks… - delete a bookmark, including one you have just added.</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>Dialog opens, deletion works, the remaining list and its thumbnails stay consistent. (There is no rename: a bookmark is named when it is added.)</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: bookmark_delete_keeps_the_list_consistent</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="n"/>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
@@ -3120,17 +3124,17 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Share location… and copy the result.</t>
+          <t>Navigate &gt; Go to location… and enter a known deep coordinate.</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Produces a shareable string/link for the current view without error.</t>
+          <t>Dialog accepts full-precision input and the view jumps exactly there (status bar matches).</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: share_string_round_trip</t>
+          <t>AUTO — cargo test: go_to_round_trips_a_deep_coordinate</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -3148,17 +3152,17 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Navigate &gt; Import .kfr… with a Kalles Fraktaler / Fraktaler-3 parameter file.</t>
+          <t>In the same dialog, enter an EXPRESSION rather than a decimal: put '-0.5 + 0.25*cos(pi/4)' in the real field and 'sqrt(2)/4' in the imaginary one, and go. Then try three that must be REFUSED: '2^i', 'sin(i)', and 'bogus(1)'.</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Import succeeds and the view lands at the imported coordinates.</t>
+          <t>The valid expressions evaluate and the view lands there; the coordinate readout shows the evaluated decimal, not the text you typed. Each invalid one is rejected with a visible message and the view does NOT move - a coordinate must never be silently half-read.</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: kfr_import_keeps_every_digit_of_a_deep_centre</t>
+          <t>AUTO — --selftest: expression functions &amp; constants</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr"/>
@@ -3176,17 +3180,17 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Open view or location… with a previously exported PNG (or .fdn).</t>
+          <t>Navigate &gt; Misiurewicz explorer… - let the gallery populate.</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>The stored view is recovered and rendered.</t>
+          <t>A grid of Misiurewicz points appears, each with a live-rendered thumbnail that resolves (no permanently blank tiles) and its multiplier readouts: octaves of zoom per repeat and degrees of twist.</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: metadata round-trips a deep view</t>
+          <t>AUTO — --uitest: misiurewicz-explorer</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr"/>
@@ -3204,18 +3208,17 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Gallery… - browse and open an entry.</t>
+          <t>In the explorer, pick a point and use it to jump (select, then solve and go).</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Gallery opens, thumbnails display, and selecting one loads that view.</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: gallery_scan_and_load
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>The solve reports progress rather than freezing the window, and the view lands on that point at depth - the landed view shows the expected shape, not a blank or interior-filled frame.</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: misiurewicz-jump-lands</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr"/>
@@ -3223,42 +3226,55 @@
       <c r="H88" s="9" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Export &amp; capture</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="7" t="n"/>
+      <c r="A89" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Locations</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Navigate &gt; Random location, several times.</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Each jump lands somewhere valid and renders real structure - not a blank or all-interior frame.</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: random-locations-coherent</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Press Ctrl+S (Snapshot) at an interesting view.</t>
+          <t>Navigate &gt; Bookmarks &gt; Add current view, then navigate away, then restore it from the menu.</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>An image is written without freezing the UI, and the app reports where it went.</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: snapshot_writes_a_file
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Bookmark is saved with a usable name and restores the exact view.</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: bookmark_round_trip</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr"/>
@@ -3267,26 +3283,26 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Open the saved snapshot in an image viewer.</t>
+          <t>Navigate &gt; Bookmarks… - delete a bookmark, including one you have just added.</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>It matches what was on screen (same framing and colours) and is not corrupt or truncated.</t>
+          <t>Dialog opens, deletion works, the remaining list and its thumbnails stay consistent. (There is no rename: a bookmark is named when it is added.)</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: snapshot-matches-the-view</t>
+          <t>AUTO — cargo test: bookmark_delete_keeps_the_list_consistent</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr"/>
@@ -3295,26 +3311,26 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>File &gt; Export image… at a LARGER size than the window (e.g. 4K) with supersampling on.</t>
+          <t>Navigate &gt; Share location… and copy the result.</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Progress is shown, the export completes, and the app stays responsive or clearly indicates it is working.</t>
+          <t>Produces a shareable string/link for the current view without error.</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: export-4k-complete</t>
+          <t>AUTO — cargo test: share_string_round_trip</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr"/>
@@ -3323,26 +3339,26 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Open the 4K export.</t>
+          <t>Navigate &gt; Import .kfr… with a Kalles Fraktaler / Fraktaler-3 parameter file.</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Full resolution, complete image, no missing tiles, no seams between tiles, no colour banding differences across tile boundaries.</t>
+          <t>Import succeeds and the view lands at the imported coordinates.</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: tiled chunked export is bit-identical</t>
+          <t>AUTO — cargo test: kfr_import_keeps_every_digit_of_a_deep_centre</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr"/>
@@ -3351,27 +3367,26 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Export &amp; capture</t>
+          <t>Locations</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Export once at a DEEP view (1e30x or deeper).</t>
+          <t>File &gt; Open view or location… with a previously exported PNG (or .fdn).</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Completes and matches the on-screen framing and colouring.</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: deep-export-matches-the-view
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>The stored view is recovered and rendered.</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --selftest: metadata round-trips a deep view</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr"/>
@@ -3379,70 +3394,71 @@
       <c r="H94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="6" t="n"/>
-      <c r="G95" s="6" t="n"/>
-      <c r="H95" s="7" t="n"/>
+      <c r="A95" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>Locations</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>File &gt; Gallery… - browse and open an entry.</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>Gallery opens, thumbnails display, and selecting one loads that view.</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: gallery_scan_and_load
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>Tools</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>Press M (Tools &gt; Find minibrot + zoom to it).</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>The app locates a minibrot and animates to it, landing on a real structure.</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --selftest: deep minibrot: size, framing, center accuracy
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Export &amp; capture</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="6" t="n"/>
+      <c r="G96" s="6" t="n"/>
+      <c r="H96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tools &gt; Newton / Misiurewicz solver… - run it on the current view.</t>
+          <t>Press Ctrl+S (Snapshot) at an interesting view.</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Solver dialog opens, runs, and reports a result without hanging.</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --selftest: Misiurewicz multiplier vs closed forms</t>
+          <t>An image is written without freezing the UI, and the app reports where it went.</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: snapshot_writes_a_file
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -3451,26 +3467,26 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tools &gt; Play tour… and play a bundled tour for at least a minute.</t>
+          <t>Open the saved snapshot in an image viewer.</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Camera moves smoothly through the script, frames resolve, captions (if any) display correctly.</t>
+          <t>It matches what was on screen (same framing and colours) and is not corrupt or truncated.</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --livetest</t>
+          <t>AUTO — --selftest: snapshot-matches-the-view</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -3479,26 +3495,26 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Close the tour player.</t>
+          <t>File &gt; Export image… at a LARGER size than the window (e.g. 4K) with supersampling on.</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Playback stops and normal interactive control returns.</t>
+          <t>Progress is shown, the export completes, and the app stays responsive or clearly indicates it is working.</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: stopping_playback_restores_interaction</t>
+          <t>AUTO — --selftest: export-4k-complete</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -3507,26 +3523,26 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tools &gt; Tour from current view… </t>
+          <t>Open the 4K export.</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Creates a tour seeded at the current view without error.</t>
+          <t>Full resolution, complete image, no missing tiles, no seams between tiles, no colour banding differences across tile boundaries.</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: generated dive script round-trips</t>
+          <t>AUTO — --selftest: tiled chunked export is bit-identical</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -3535,26 +3551,27 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Tools</t>
+          <t>Export &amp; capture</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tools &gt; Benchmark… and let it finish.</t>
+          <t>Export once at a DEEP view (1e30x or deeper).</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Benchmark runs to completion and reports results; app remains usable afterwards.</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --benchmark-std</t>
+          <t>Completes and matches the on-screen framing and colouring.</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: deep-export-matches-the-view
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -3564,7 +3581,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="B102" s="6" t="n"/>
@@ -3577,26 +3594,26 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Press F1 (Help &amp; reference).</t>
+          <t>Press M (Tools &gt; Find minibrot + zoom to it).</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Help window opens, content is readable and scrolls, no broken layout or missing sections.</t>
+          <t>The app locates a minibrot and animates to it, landing on a real structure.</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>PARTLY AUTO — cargo test: help_sections_all_render
+          <t>PARTLY AUTO — --selftest: deep minibrot: size, framing, center accuracy
 Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
@@ -3606,26 +3623,26 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Diagnostics… </t>
+          <t>Tools &gt; Newton / Misiurewicz solver… - run it on the current view.</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location), including a 'Deep-zoom arithmetic' line naming the backend in use.</t>
+          <t>Solver dialog opens, runs, and reports a result without hanging.</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --uitest: diagnostics-populated</t>
+          <t>AUTO — --selftest: Misiurewicz multiplier vs closed forms</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr"/>
@@ -3634,26 +3651,26 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; About (the last Help section). Read the 'Deep-zoom arithmetic' line.</t>
+          <t>Tools &gt; Play tour… and play a bundled tour for at least a minute.</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Names the arithmetic that has actually run and what the build contains. On the standard build: astro-float. On the accelerated build: rug, with the MPFR/GMP versions. Before any deep render it may say none has run yet - that is correct, not a missing value.</t>
+          <t>Camera moves smoothly through the script, frames resolve, captions (if any) display correctly.</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: about_names_the_running_backend</t>
+          <t>AUTO — CLI: --livetest</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr"/>
@@ -3662,26 +3679,26 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Faster deep zoom… </t>
+          <t>Close the tour player.</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>On the STANDARD build: explains the optional accelerated download and offers two buttons. 'Download for this version' opens a URL containing THIS version's tag; 'All releases' opens the releases page. On the ACCELERATED build: says you are already running it instead, and offers no download.</t>
+          <t>Playback stops and normal interactive control returns.</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: accelerated_asset_url</t>
+          <t>AUTO — cargo test: stopping_playback_restores_interaction</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr"/>
@@ -3690,26 +3707,26 @@
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help &gt; Report an issue… </t>
+          <t xml:space="preserve">Tools &gt; Tour from current view… </t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
+          <t>Creates a tour seeded at the current view without error.</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: issue_url_is_well_formed</t>
+          <t>AUTO — --selftest: generated dive script round-trips</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr"/>
@@ -3718,26 +3735,26 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Help &amp; settings</t>
+          <t>Tools</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; Check for updates.</t>
+          <t>Tools &gt; Benchmark… and let it finish.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
+          <t>Benchmark runs to completion and reports results; app remains usable afterwards.</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: update_check_reaches_a_verdict</t>
+          <t>AUTO — CLI: --benchmark-std</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr"/>
@@ -3745,69 +3762,70 @@
       <c r="H108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>Help &amp; settings</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>File &gt; Settings - change a setting, close and reopen the menu.</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>Setting persists and takes effect.</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: a_setting_survives_save_and_reload</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr"/>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="6" t="n"/>
+      <c r="G109" s="6" t="n"/>
+      <c r="H109" s="7" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>Linux</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="6" t="n"/>
-      <c r="H110" s="7" t="n"/>
+      <c r="A110" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Help &amp; settings</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Press F1 (Help &amp; reference).</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Help window opens, content is readable and scrolls, no broken layout or missing sections.</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: help_sections_all_render
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Move ~/.config/Fractadyne aside (that is where `directories::ProjectDirs` puts the profile; $XDG_CONFIG_HOME overrides it) and launch the extracted tarball's ./fractadyne.</t>
+          <t xml:space="preserve">Help &gt; Diagnostics… </t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>True first run: welcome dialog, home view, no console errors. On exit a new ~/.config/Fractadyne/session.toml exists — state belongs in the user profile, never beside the binary, so an extracted folder stays disposable.</t>
+          <t>Diagnostics window opens and shows real values (GPU/adapter, paths, log location), including a 'Deep-zoom arithmetic' line naming the backend in use.</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
+          <t>AUTO — --uitest: diagnostics-populated</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr"/>
@@ -3816,26 +3834,26 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>From the extracted tarball run ./fractadyne --selftest and read the goldens section.</t>
+          <t>Help &gt; About (the last Help section). Read the 'Deep-zoom arithmetic' line.</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>It runs to a verdict. Goldens are compared with the CROSS-GPU tolerance, not the strict one, because validation/golden/BLESSED-GPU.txt ships in the tarball — if the run reports strict failures on a non-3080 card, that file is missing from the package and every Linux tester will see expected vendor variance as a failure.</t>
+          <t>Names the arithmetic that has actually run and what the build contains. On the standard build: astro-float. On the accelerated build: rug, with the MPFR/GMP versions. Before any deep render it may say none has run yet - that is correct, not a missing value.</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --selftest</t>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr"/>
@@ -3844,26 +3862,26 @@
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Run ./fractadyne --selftest --selftest-filter live-res, then read the adapter line in the log: 'capability: TIMESTAMP_QUERY=true|false'.</t>
+          <t xml:space="preserve">Help &gt; Faster deep zoom… </t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>The settled-resolution invariant passes WHATEVER that capability says. This is the point of running it here: TIMESTAMP_QUERY is genuinely absent on the GL backend and on several Mesa/RADV/ANV combinations, and until now that path had only ever been faked on an NVIDIA card with FRACTADYNE_NO_TIMESTAMPS=1. A view stuck at ~1/3 resolution forever is the failure.</t>
+          <t>On the STANDARD build: explains the optional accelerated download and offers two buttons. 'Download for this version' opens a URL containing THIS version's tag; 'All releases' opens the releases page. On the ACCELERATED build: says you are already running it instead, and offers no download.</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --selftest: live-res</t>
+          <t>AUTO — cargo test: accelerated_asset_url</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr"/>
@@ -3872,26 +3890,26 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Repeat the launch on each GPU the rig can take (NVIDIA / AMD / Intel), recording for each: the adapter line, the chosen backend, and whether deep views render correctly.</t>
+          <t xml:space="preserve">Help &gt; Report an issue… </t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Every card opens a window and renders. Record the adapter + backend per card — cross-vendor differences in the deep floatexp path are a known open bug (3080 all-black vs 3070 rich), so this is evidence-gathering as much as pass/fail.</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+          <t>Opens the issue reporting path correctly (browser or dialog) with the app's details.</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: issue_url_is_well_formed</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr"/>
@@ -3900,26 +3918,26 @@
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Run once under Wayland and once under X11 (log into an X11 session, or unset WAYLAND_DISPLAY so winit falls back).</t>
+          <t>Help &gt; Check for updates.</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Window opens, resizes, and scales sensibly under both. Note any difference in DPI handling, cursor behaviour or window decorations.</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+          <t>Performs a check and reports a clear result (up to date, or an update is available). No hang.</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: update_check_reaches_a_verdict</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr"/>
@@ -3928,26 +3946,26 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Help &amp; settings</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; Diagnostics — check the four readings that have platform-specific implementations: process memory (/proc/self/status), free disk (statvfs), CPU topology (/proc/cpuinfo), and GPU VRAM (amdgpu sysfs, else nvidia-smi).</t>
+          <t>File &gt; Settings - change a setting, close and reopen the menu.</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>All four report PLAUSIBLE, non-zero values that match what the system tools say. These were written for Linux and verified only to compile, so a zero or an absurd figure here is a real defect, not a cosmetic one.</t>
+          <t>Setting persists and takes effect.</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --uitest: diagnostics-populated</t>
+          <t>AUTO — cargo test: a_setting_survives_save_and_reload</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr"/>
@@ -3955,32 +3973,18 @@
       <c r="H116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>Linux</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>Exercise the native file dialogs: File &gt; Open view or location…, and an export that asks for a path.</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>The GTK dialogs open, are navigable, and the chosen path is honoured. A missing GTK runtime shows up here first.</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr"/>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="9" t="inlineStr"/>
+      <c r="B117" s="6" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="6" t="n"/>
+      <c r="F117" s="6" t="n"/>
+      <c r="G117" s="6" t="n"/>
+      <c r="H117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
@@ -3993,17 +3997,17 @@
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Run on a box with no audio server (or with FRACTADYNE_NO_SOUND=1) and let a long render finish.</t>
+          <t>Move ~/.config/Fractadyne aside (that is where `directories::ProjectDirs` puts the profile; $XDG_CONFIG_HOME overrides it) and launch the extracted tarball's ./fractadyne.</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>No crash, no hang, and no error spew when the finish tone cannot play — audio is a nicety and must never be able to take the app down.</t>
+          <t>True first run: welcome dialog, home view, no console errors. On exit a new ~/.config/Fractadyne/session.toml exists — state belongs in the user profile, never beside the binary, so an extracted folder stays disposable.</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --no-sound</t>
+          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
         </is>
       </c>
       <c r="F118" s="9" t="inlineStr"/>
@@ -4021,18 +4025,17 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Run ./fractadyne --version over SSH with no DISPLAY set.</t>
+          <t>From the extracted tarball run ./fractadyne --selftest and read the goldens section.</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Prints 'fractadyne &lt;version&gt; (build N)' and exits cleanly without trying to open a window. The version must match the tag being reviewed.</t>
-        </is>
-      </c>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: title_string_matches_version
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>It runs to a verdict. Goldens are compared with the CROSS-GPU tolerance, not the strict one, because validation/golden/BLESSED-GPU.txt ships in the tarball — if the run reports strict failures on a non-3080 card, that file is missing from the package and every Linux tester will see expected vendor variance as a failure.</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --selftest</t>
         </is>
       </c>
       <c r="F119" s="9" t="inlineStr"/>
@@ -4050,17 +4053,17 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>After the session above, check ~/.config/Fractadyne/logs/ for crash-*.txt.</t>
+          <t>Run ./fractadyne --selftest --selftest-filter live-res, then read the adapter line in the log: 'capability: TIMESTAMP_QUERY=true|false'.</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>No new crash reports. (If any exist this run FAILS and the file must be attached — the log directory is the Linux equivalent of the Windows config\logs folder checked earlier.)</t>
+          <t>The settled-resolution invariant passes WHATEVER that capability says. This is the point of running it here: TIMESTAMP_QUERY is genuinely absent on the GL backend and on several Mesa/RADV/ANV combinations, and until now that path had only ever been faked on an NVIDIA card with FRACTADYNE_NO_TIMESTAMPS=1. A view stuck at ~1/3 resolution forever is the failure.</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>AUTO — --uitest: no-crash-files</t>
+          <t>AUTO — --selftest: live-res</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -4068,41 +4071,55 @@
       <c r="H120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Accelerated build</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="n"/>
-      <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
-      <c r="G121" s="6" t="n"/>
-      <c r="H121" s="7" t="n"/>
+      <c r="A121" s="8" t="n">
+        <v>107</v>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Repeat the launch on each GPU the rig can take (NVIDIA / AMD / Intel), recording for each: the adapter line, the chosen backend, and whether deep views render correctly.</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>Every card opens a window and renders. Record the adapter + backend per card — cross-vendor differences in the deep floatexp path are a known open bug (3080 all-black vs 3070 rich), so this is evidence-gathering as much as pass/fail.</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr"/>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>WINDOWS: extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
+          <t>Run once under Wayland and once under X11 (log into an X11 session, or unset WAYLAND_DISPLAY so winit falls back).</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
-        </is>
-      </c>
-      <c r="E122" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — script: scripts/build-accelerated.ps1</t>
+          <t>Window opens, resizes, and scales sensibly under both. Note any difference in DPI handling, cursor behaviour or window decorations.</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -4111,26 +4128,26 @@
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>LINUX: extract fractadyne-&lt;tag&gt;-linux-x64-accelerated.tar.gz to a new folder on a distro with glibc 2.39+ (Ubuntu 24.04+, Debian 13+) and run ./fractadyne from it. Use a machine with only the RUNTIME libraries (libgmp10, libmpfr6) - no -dev packages, no build tools.</t>
+          <t>Help &gt; Diagnostics — check the four readings that have platform-specific implementations: process memory (/proc/self/status), free disk (statvfs), CPU topology (/proc/cpuinfo), and GPU VRAM (amdgpu sysfs, else nvidia-smi).</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Window opens normally. This package deliberately does NOT bundle GMP/MPFR, so it must find the system ones; a missing-library error here means the packaging assumed something the target does not have.</t>
+          <t>All four report PLAUSIBLE, non-zero values that match what the system tools say. These were written for Linux and verified only to compile, so a zero or an absurd figure here is a real defect, not a cosmetic one.</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>AUTO — script: scripts/build-accelerated.sh</t>
+          <t>AUTO — --uitest: diagnostics-populated</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -4139,21 +4156,21 @@
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>LINUX: run the same tarball on an OLDER distro (Ubuntu 22.04 / Debian 12).</t>
+          <t>Exercise the native file dialogs: File &gt; Open view or location…, and an export that asks for a path.</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>It refuses to start with a clear glibc / missing-symbol message - and the STANDARD linux-x64.tar.gz still runs there. The accelerated package has a higher floor by construction (its GMP requirement forces a newer build host); what must not happen is a confusing failure with no standard build to fall back to.</t>
+          <t>The GTK dialogs open, are navigable, and the chosen path is honoured. A missing GTK runtime shows up here first.</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -4167,26 +4184,26 @@
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>On the accelerated build, open Help &gt; Faster deep zoom and read the download link it offers (hover it if the text is elided).</t>
+          <t>Run on a box with no audio server (or with FRACTADYNE_NO_SOUND=1) and let a long render finish.</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>It names the package for the platform you are running - .zip on Windows, .tar.gz on Linux - and the version matches the running build. Offering the other platform's file is a dead download even though the link resolves.</t>
+          <t>No crash, no hang, and no error spew when the finish tone cannot play — audio is a nicety and must never be able to take the app down.</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: the_url_names_this_platforms_package</t>
+          <t>AUTO — CLI: --no-sound</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -4195,26 +4212,27 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Help &gt; About on that build.</t>
+          <t>Run ./fractadyne --version over SSH with no DISPLAY set.</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
-        </is>
-      </c>
-      <c r="E126" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — cargo test: about_names_the_running_backend</t>
+          <t>Prints 'fractadyne &lt;version&gt; (build N)' and exits cleanly without trying to open a window. The version must match the tag being reviewed.</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: title_string_matches_version
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -4223,26 +4241,26 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Accelerated build</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Check that your existing locations, bookmarks and last session are present.</t>
+          <t>After the session above, check ~/.config/Fractadyne/logs/ for crash-*.txt.</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
+          <t>No new crash reports. (If any exist this run FAILS and the file must be attached — the log directory is the Linux equivalent of the Windows config\logs folder checked earlier.)</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
+          <t>AUTO — --uitest: no-crash-files</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -4250,33 +4268,18 @@
       <c r="H127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Accelerated build</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
-        </is>
-      </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
-        </is>
-      </c>
-      <c r="E128" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="inlineStr"/>
-      <c r="G128" s="8" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="6" t="n"/>
+      <c r="F128" s="6" t="n"/>
+      <c r="G128" s="6" t="n"/>
+      <c r="H128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
@@ -4289,17 +4292,17 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
+          <t>WINDOWS: extract fractadyne-&lt;tag&gt;-windows-x64-accelerated.zip to a NEW folder and run fractadyne.exe from it. Do this on a machine (or account) with no MSYS2 and no MinGW on PATH.</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
+          <t>Window opens normally. NO 'the code execution cannot proceed' or missing-DLL dialog - the package must be self-contained apart from the .dll files beside the executable.</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>AUTO — CLI: --bench-bignum</t>
+          <t>AUTO — script: scripts/build-accelerated.ps1</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr"/>
@@ -4317,17 +4320,17 @@
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>WINDOWS: delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after. (LINUX equivalent: temporarily move the tarball to a machine without libmpfr6.)</t>
+          <t>LINUX: extract fractadyne-&lt;tag&gt;-linux-x64-accelerated.tar.gz to a new folder on a distro with glibc 2.39+ (Ubuntu 24.04+, Debian 13+) and run ./fractadyne from it. Use a machine with only the RUNTIME libraries (libgmp10, libmpfr6) - no -dev packages, no build tools.</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Fails to start with a missing-library error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+          <t>Window opens normally. This package deliberately does NOT bundle GMP/MPFR, so it must find the system ones; a missing-library error here means the packaging assumed something the target does not have.</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — script: scripts/build-accelerated.sh</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr"/>
@@ -4345,17 +4348,17 @@
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>On the PUBLISHED release page, compare the 'Which download?' table against the Assets list at the foot of the page.</t>
+          <t>LINUX: run the same tarball on an OLDER distro (Ubuntu 22.04 / Debian 12).</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Every attached asset has a row, and every row names an attached asset. The table is written by hand and the asset list is produced by the build jobs, so they drift silently: v0.2.41-beta.20 shipped the Linux accelerated tarball attached but unlisted, which reads to a visitor exactly like a build that failed.</t>
-        </is>
-      </c>
-      <c r="E131" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>It refuses to start with a clear glibc / missing-symbol message - and the STANDARD linux-x64.tar.gz still runs there. The accelerated package has a higher floor by construction (its GMP requirement forces a newer build host); what must not happen is a confusing failure with no standard build to fall back to.</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr"/>
@@ -4363,42 +4366,55 @@
       <c r="H131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Persistence</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="n"/>
-      <c r="C132" s="6" t="n"/>
-      <c r="D132" s="6" t="n"/>
-      <c r="E132" s="6" t="n"/>
-      <c r="F132" s="6" t="n"/>
-      <c r="G132" s="6" t="n"/>
-      <c r="H132" s="7" t="n"/>
+      <c r="A132" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>On the accelerated build, open Help &gt; Faster deep zoom and read the download link it offers (hover it if the text is elided).</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>It names the package for the platform you are running - .zip on Windows, .tar.gz on Linux - and the version matches the running build. Offering the other platform's file is a dead download even though the link resolves.</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: the_url_names_this_platforms_package</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr"/>
+      <c r="G132" s="8" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
+          <t>Help &gt; About on that build.</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — --uitest: clean-exit-marker
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>'Deep-zoom arithmetic' names rug and reports the MPFR and GMP versions.</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: about_names_the_running_backend</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr"/>
@@ -4407,26 +4423,26 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Relaunch the app.</t>
+          <t>Check that your existing locations, bookmarks and last session are present.</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+          <t>All there. Settings live in the user profile, not beside the executable, so the two builds share them and nothing needs importing.</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
+          <t>AUTO — cargo test: config_lives_in_the_user_profile</t>
         </is>
       </c>
       <c r="F134" s="9" t="inlineStr"/>
@@ -4435,26 +4451,27 @@
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Persistence</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Check the profile's logs folder for crash-*.txt files created during this run (Windows: %APPDATA%\Fractadyne\Fractadyne\config\logs; Linux: ~/.config/Fractadyne/logs).</t>
+          <t>Open the same deep location (1e50 or deeper) in BOTH builds and compare the images side by side; export a PNG from each if unsure.</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — --uitest: no-crash-files</t>
+          <t>Visually identical. The two backends are byte-identical by construction and by test, so ANY visible difference is a bug worth stopping the release for.</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: identity_holds_where_the_multiply_algorithms_diverge
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr"/>
@@ -4462,41 +4479,55 @@
       <c r="H135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="n"/>
-      <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6" t="n"/>
-      <c r="E136" s="6" t="n"/>
-      <c r="F136" s="6" t="n"/>
-      <c r="G136" s="6" t="n"/>
-      <c r="H136" s="7" t="n"/>
+      <c r="A136" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>Accelerated build</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Dive into a deep view on both builds and watch the pause before the picture starts resolving (the reference-orbit build).</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Noticeably shorter on the accelerated build. This is the only user-visible difference there should be. Note both timings.</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --bench-bignum</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr"/>
+      <c r="G136" s="8" t="inlineStr"/>
+      <c r="H136" s="9" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+          <t>WINDOWS: delete libmpfr-6.dll from the accelerated folder and try to launch it. Restore it after. (LINUX equivalent: temporarily move the tarball to a machine without libmpfr6.)</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --soak</t>
+          <t>Fails to start with a missing-library error rather than silently falling back to the slow arithmetic. Restoring the file makes it work again.</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr"/>
@@ -4505,27 +4536,26 @@
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Accelerated build</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>With the view fully settled and the mouse OFF the window, watch the performance panel's activity line and your GPU/fan (Task Manager's GPU column, or nvidia-smi / radeontop) for a minute.</t>
+          <t>On the PUBLISHED release page, compare the 'Which download?' table against the Assets list at the foot of the page.</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>The activity line reads 'idle' AND the app stops drawing: GPU usage falls to ~0 and STAYS there. A steady 1-4 fps trickle on a static picture is the defect fixed in beta.18 - the app was re-rendering a finished frame forever. Touch the window and it must wake instantly. FRACTADYNE_TRACE=idle names whatever is holding it awake if this fails.</t>
-        </is>
-      </c>
-      <c r="E138" s="10" t="inlineStr">
-        <is>
-          <t>PARTLY AUTO — cargo test: both_views_quiet_and_nothing_animating_is_quiescent
-Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+          <t>Every attached asset has a row, and every row names an attached asset. The table is written by hand and the asset list is produced by the build jobs, so they drift silently: v0.2.41-beta.20 shipped the Linux accelerated tarball attached but unlisted, which reads to a visitor exactly like a build that failed.</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F138" s="9" t="inlineStr"/>
@@ -4533,55 +4563,41 @@
       <c r="H138" s="9" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="n">
-        <v>122</v>
-      </c>
-      <c r="B139" s="9" t="inlineStr">
-        <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="inlineStr">
-        <is>
-          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
-        </is>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
-        <is>
-          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
-        </is>
-      </c>
-      <c r="E139" s="11" t="inlineStr">
-        <is>
-          <t>AUTO — CLI: --torture</t>
-        </is>
-      </c>
-      <c r="F139" s="9" t="inlineStr"/>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="9" t="inlineStr"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+      <c r="E139" s="6" t="n"/>
+      <c r="F139" s="6" t="n"/>
+      <c r="G139" s="6" t="n"/>
+      <c r="H139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Persistence</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+          <t>Navigate to a distinctive deep view, then quit via File &gt; Quit.</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>No crash and no stuck frame; the final selection is what renders.</t>
+          <t>App exits cleanly - no hang, no crash dialog, no lingering process.</t>
         </is>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
-          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
+          <t>PARTLY AUTO — --uitest: clean-exit-marker
 Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
@@ -4590,70 +4606,254 @@
       <c r="H140" s="9" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Sign-off</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="n"/>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6" t="n"/>
-      <c r="E141" s="6" t="n"/>
-      <c r="F141" s="6" t="n"/>
-      <c r="G141" s="6" t="n"/>
-      <c r="H141" s="7" t="n"/>
+      <c r="A141" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Relaunch the app.</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>It reopens on the SAME view you left, with the same fractal, palette and settings.</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — cargo test: a_deep_view_and_its_colouring_survive_a_restart</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr"/>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Persistence</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+          <t>Check the profile's logs folder for crash-*.txt files created during this run (Windows: %APPDATA%\Fractadyne\Fractadyne\config\logs; Linux: ~/.config/Fractadyne/logs).</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>No new crash reports. (If any exist, this run FAILS and the file must be attached.)</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: no-crash-files</t>
         </is>
       </c>
       <c r="F142" s="9" t="inlineStr"/>
       <c r="G142" s="8" t="inlineStr"/>
       <c r="H142" s="9" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+      <c r="E143" s="6" t="n"/>
+      <c r="F143" s="6" t="n"/>
+      <c r="G143" s="6" t="n"/>
+      <c r="H143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Leave the app running idle at a deep view for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>No creeping memory growth to the point of instability, no watchdog restart, view still correct.</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --soak</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr"/>
+      <c r="G144" s="8" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>With the view fully settled and the mouse OFF the window, watch the performance panel's activity line and your GPU/fan (Task Manager's GPU column, or nvidia-smi / radeontop) for a minute.</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>The activity line reads 'idle' AND the app stops drawing: GPU usage falls to ~0 and STAYS there. A steady 1-4 fps trickle on a static picture is the defect fixed in beta.18 - the app was re-rendering a finished frame forever. Touch the window and it must wake instantly. FRACTADYNE_TRACE=idle names whatever is holding it awake if this fails.</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: both_views_quiet_and_nothing_animating_is_quiescent
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr"/>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="9" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Do a fast, sustained zoom-in / zoom-out / pan session for ~2 minutes.</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>No freeze, no device-loss restart, no crash. The app keeps up or degrades gracefully.</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — CLI: --torture</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr"/>
+      <c r="G146" s="8" t="inlineStr"/>
+      <c r="H146" s="9" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="n">
+        <v>130</v>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>Switch fractal type, colour method and palette rapidly several times in a row.</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>No crash and no stuck frame; the final selection is what renders.</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: rapid-switching-settles-on-the-final-choice
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr"/>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="n"/>
+      <c r="C148" s="6" t="n"/>
+      <c r="D148" s="6" t="n"/>
+      <c r="E148" s="6" t="n"/>
+      <c r="F148" s="6" t="n"/>
+      <c r="G148" s="6" t="n"/>
+      <c r="H148" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr"/>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H142"/>
+  <autoFilter ref="A1:H149"/>
   <mergeCells count="17">
-    <mergeCell ref="A136:H136"/>
+    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A109:H109"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A139:H139"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A148:H148"/>
+    <mergeCell ref="A128:H128"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A132:H132"/>
-    <mergeCell ref="A110:H110"/>
-    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A117:H117"/>
+    <mergeCell ref="A84:H84"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="G2:G149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -772,7 +772,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>81 of 131 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
+          <t>81 of 139 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
         </is>
       </c>
     </row>
@@ -786,14 +786,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>38 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
+          <t>41 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10 need a person outright, and 2 is a process step.</t>
+          <t>15 need a person outright, and 2 is a process step.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4792,7 +4792,7 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Palette interchange</t>
         </is>
       </c>
       <c r="B148" s="6" t="n"/>
@@ -4809,31 +4809,272 @@
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Palette interchange</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+          <t>In the gradient editor, build or load a gradient, give it a name and press 'Save .ggr…'. Then press 'Import .ggr…' and load the file you just wrote.</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
-        </is>
-      </c>
-      <c r="E149" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>It comes back looking identical - same colours, same midpoints, same curves. The editor does NOT report it as approximated unless a segment uses a Bézier curve you actually bent.</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: a_ggr_written_here_reads_back_identically
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
       <c r="G149" s="8" t="inlineStr"/>
       <c r="H149" s="9" t="inlineStr"/>
     </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>⭐Open that exported .ggr in GIMP (drop it in the gradients folder, or File ▸ Open in the Gradients dock) and compare it with the editor's preview bar side by side. Mark BLOCKED if GIMP is not available.</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>GIMP lists it, the name is the one you typed, and the ramp matches ours - including where each midpoint sits and where a curved segment bends. This is the one direction no test here can check: our round trip parses our own output with our own parser, which would agree with itself even if the format were wrong.</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr"/>
+      <c r="G150" s="8" t="inlineStr"/>
+      <c r="H150" s="9" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>⭐Open the SAME file in a second application that reads .ggr - Krita (Gradients docker) or Inkscape. Mark BLOCKED if neither is available.</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>It loads and matches. A second reader matters because GIMP authored this format and is forgiving of files shaped the way it writes them; a second implementation is where a tolerated quirk shows up as a difference.</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr"/>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="9" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>In the editor set one segment's Curve to Bézier and drag a control point well off the diagonal, then 'Save .ggr…' again and re-import it.</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>The save message NAMES how many segments it had to approximate. On re-import those segments are straight blends, and the shape you drew is gone. That is the format's limit, not a bug - what is being checked is that it SAID so rather than flattening in silence.</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: an_unbent_bezier_exports_as_linear_and_a_bent_one_is_reported
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr"/>
+      <c r="G152" s="8" t="inlineStr"/>
+      <c r="H152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>⭐In GIMP, author a gradient that uses a curved (not linear) segment, an HSV-anticlockwise segment and a midpoint dragged well off centre. Save it and import it here. Mark BLOCKED if GIMP is not available.</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>All three survive: the curve bends the same way, the hue sweep goes the long way round, and the midpoint sits where GIMP put it. ⚠Every .ggr fixture in the test suite was written by this repo, so a file authored elsewhere is the only real test of the parser.</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr"/>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="9" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>136</v>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>⭐Load a .ugr gradient that carries a 'rotation=' value, and compare the result against the same gradient shown in Ultra Fractal. Mark BLOCKED if Ultra Fractal is not available.</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>The colours are rotated the same way round. ⚠The rotation is applied but its DIRECTION has never been checked against the source application - a sign error here still produces a plausible palette, which is why only a comparison can catch it.</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr"/>
+      <c r="G154" s="8" t="inlineStr"/>
+      <c r="H154" s="9" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>⭐Import a real Adobe .ase swatch file - one exported from Photoshop or Illustrator, not one written for this test. Mark BLOCKED if you have none.</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>It loads as an evenly spaced gradient, OR is rejected with a specific reason. ⚠Either outcome is information: this is the ONE importer written from the published layout rather than against a real file, and its own fixtures share the parser's understanding of the format. A rejection is worth reporting, not working around.</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>MANUAL — needs a person (see design/checklist-automation.md)</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr"/>
+      <c r="G155" s="8" t="inlineStr"/>
+      <c r="H155" s="9" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="n">
+        <v>138</v>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>Palette interchange</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>Save a gradient into the library (type a name, press Save), quit the application, relaunch it, open the gradient editor and load that entry from the 'Saved' menu.</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>It is still there after the restart and comes back with its curves, midpoints and colour spaces intact - not flattened to plain stops.</t>
+        </is>
+      </c>
+      <c r="E156" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: a_saved_gradient_round_trips_through_toml_without_flattening
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr"/>
+      <c r="G156" s="8" t="inlineStr"/>
+      <c r="H156" s="9" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="F157" s="6" t="n"/>
+      <c r="G157" s="6" t="n"/>
+      <c r="H157" s="7" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr"/>
+      <c r="G158" s="8" t="inlineStr"/>
+      <c r="H158" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H149"/>
-  <mergeCells count="17">
+  <autoFilter ref="A1:H158"/>
+  <mergeCells count="18">
     <mergeCell ref="A143:H143"/>
     <mergeCell ref="A78:H78"/>
     <mergeCell ref="A30:H30"/>
@@ -4846,6 +5087,7 @@
     <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A148:H148"/>
+    <mergeCell ref="A157:H157"/>
     <mergeCell ref="A128:H128"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A102:H102"/>
@@ -4853,7 +5095,7 @@
     <mergeCell ref="A84:H84"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="G2:G158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/validation/release-checklist.xlsx
+++ b/validation/release-checklist.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Run" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Run'!$A$1:$H$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -772,7 +772,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>81 of 139 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
+          <t>82 of 143 steps are FULLY automated - a machine check fails if the behaviour breaks.</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>41 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
+          <t>44 are PARTLY automated - the effect is checked; the gesture and the appearance are yours.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5033,7 +5033,7 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Reference cache</t>
         </is>
       </c>
       <c r="B157" s="6" t="n"/>
@@ -5050,52 +5050,182 @@
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>Sign-off</t>
+          <t>Reference cache</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+          <t>Open a deep location (validation/spiral-9.98e60205.fdn, or any view past ~1e1000) and let it finish its reference build. Quit, relaunch, and open the SAME location again; then zoom or pan a little way from it.</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
-        </is>
-      </c>
-      <c r="E158" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>The second visit renders in seconds, not minutes - the log carries an 'orbit cache HIT' line and no long 'building reference' phase - and the nearby view reuses the same orbit (another HIT, no rebuild). The picture is the one the first visit showed.</t>
+        </is>
+      </c>
+      <c r="E158" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — --selftest: an orbit from the disk cache renders the same as a fresh pick
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr"/>
       <c r="G158" s="8" t="inlineStr"/>
       <c r="H158" s="9" t="inlineStr"/>
     </row>
+    <row r="159">
+      <c r="A159" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>Reference cache</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>File &gt; Settings &gt; Reference cache... . Press 'Open folder'.</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>The window shows the cache's folder path, a usage bar against the limit with the orbit count, and the orbits it holds (iterations, precision, size, last used). 'Open folder' opens that folder in the file manager and the .orbit files are there.</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>AUTO — --uitest: reference-cache</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="inlineStr"/>
+      <c r="G159" s="8" t="inlineStr"/>
+      <c r="H159" s="9" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>Reference cache</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>Set the limit BELOW the current usage (drag the MB value down).</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>Usage drops under the new limit at once. What went was the CHEAPEST orbits (short, shallow); the deep one from the first row is still listed - a stream of quick entries must never displace the hour-long one.</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: eviction_drops_the_cheapest_orbit_not_the_oldest
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="inlineStr"/>
+      <c r="G160" s="8" t="inlineStr"/>
+      <c r="H160" s="9" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="n">
+        <v>142</v>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>Reference cache</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>Press 'Clear cache...'. Cancel once; then do it again and confirm.</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>It asks first (Cancel first, the red Delete second). After Delete the usage reads 0 orbits, the folder is empty, and the next visit to the deep location rebuilds its reference (slow again) - clearing cost time, not data.</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>PARTLY AUTO — cargo test: clear_removes_every_entry_and_stray_temp_files
+Still yours: whatever the machine cannot judge — see design/checklist-automation.md.</t>
+        </is>
+      </c>
+      <c r="F161" s="9" t="inlineStr"/>
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="9" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="n"/>
+      <c r="C162" s="6" t="n"/>
+      <c r="D162" s="6" t="n"/>
+      <c r="E162" s="6" t="n"/>
+      <c r="F162" s="6" t="n"/>
+      <c r="G162" s="6" t="n"/>
+      <c r="H162" s="7" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>Review every FAIL and BLOCKED row above with the release decision in mind.</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>Either all rows PASS, or each non-PASS has an agreed decision (fix before release / accept and document). Record the decision on the Cover sheet.</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr"/>
+      <c r="G163" s="8" t="inlineStr"/>
+      <c r="H163" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H158"/>
-  <mergeCells count="18">
+  <autoFilter ref="A1:H163"/>
+  <mergeCells count="19">
     <mergeCell ref="A143:H143"/>
-    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A148:H148"/>
+    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A139:H139"/>
     <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A139:H139"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A96:H96"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A148:H148"/>
-    <mergeCell ref="A157:H157"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A102:H102"/>
     <mergeCell ref="A117:H117"/>
-    <mergeCell ref="A84:H84"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G158" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
+    <dataValidation sqref="G2:G163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose PASS, FAIL, BLOCKED or N-A." type="list">
       <formula1>"PASS,FAIL,BLOCKED,N-A"</formula1>
     </dataValidation>
   </dataValidations>
